--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121333575</v>
+        <v>121333520</v>
       </c>
       <c r="B2" t="n">
-        <v>78334</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461081</v>
+        <v>461096</v>
       </c>
       <c r="R2" t="n">
-        <v>6872891</v>
+        <v>6872904</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121333520</v>
+        <v>121333407</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461096</v>
+        <v>461111</v>
       </c>
       <c r="R3" t="n">
-        <v>6872904</v>
+        <v>6872947</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121333407</v>
+        <v>121333575</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461111</v>
+        <v>461081</v>
       </c>
       <c r="R4" t="n">
-        <v>6872947</v>
+        <v>6872891</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121333407</v>
+        <v>121333575</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461111</v>
+        <v>461081</v>
       </c>
       <c r="R3" t="n">
-        <v>6872947</v>
+        <v>6872891</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121333575</v>
+        <v>121333407</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461081</v>
+        <v>461111</v>
       </c>
       <c r="R4" t="n">
-        <v>6872891</v>
+        <v>6872947</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121333520</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121333575</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>121333407</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121333520</v>
+        <v>121333407</v>
       </c>
       <c r="B2" t="n">
         <v>79685</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461096</v>
+        <v>461111</v>
       </c>
       <c r="R2" t="n">
-        <v>6872904</v>
+        <v>6872947</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121333407</v>
+        <v>121333520</v>
       </c>
       <c r="B4" t="n">
         <v>79685</v>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461111</v>
+        <v>461096</v>
       </c>
       <c r="R4" t="n">
-        <v>6872947</v>
+        <v>6872904</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121333407</v>
+        <v>121333575</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>78343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461111</v>
+        <v>461081</v>
       </c>
       <c r="R2" t="n">
-        <v>6872947</v>
+        <v>6872891</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121333575</v>
+        <v>121333407</v>
       </c>
       <c r="B3" t="n">
-        <v>78340</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461081</v>
+        <v>461111</v>
       </c>
       <c r="R3" t="n">
-        <v>6872891</v>
+        <v>6872947</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121333520</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121333575</v>
+        <v>121333407</v>
       </c>
       <c r="B2" t="n">
-        <v>78343</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461081</v>
+        <v>461111</v>
       </c>
       <c r="R2" t="n">
-        <v>6872891</v>
+        <v>6872947</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121333407</v>
+        <v>121333520</v>
       </c>
       <c r="B3" t="n">
         <v>79688</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461111</v>
+        <v>461096</v>
       </c>
       <c r="R3" t="n">
-        <v>6872947</v>
+        <v>6872904</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121333520</v>
+        <v>121333575</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>78343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461096</v>
+        <v>461081</v>
       </c>
       <c r="R4" t="n">
-        <v>6872904</v>
+        <v>6872891</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121333407</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121333520</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>121333575</v>
       </c>
       <c r="B4" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,6 +984,414 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121587612</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78643</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>185</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>460706</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6873222</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121587355</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78643</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>185</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>460722</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6873319</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121587377</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78691</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>864</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>460722</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6873319</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121587594</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78345</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>460711</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6873214</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121333407</v>
+        <v>121333520</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461111</v>
+        <v>461096</v>
       </c>
       <c r="R2" t="n">
-        <v>6872947</v>
+        <v>6872904</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121333520</v>
+        <v>121333575</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>78345</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461096</v>
+        <v>461081</v>
       </c>
       <c r="R3" t="n">
-        <v>6872904</v>
+        <v>6872891</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121333575</v>
+        <v>121333407</v>
       </c>
       <c r="B4" t="n">
-        <v>78344</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461081</v>
+        <v>461111</v>
       </c>
       <c r="R4" t="n">
-        <v>6872891</v>
+        <v>6872947</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587612</v>
+        <v>121587594</v>
       </c>
       <c r="B5" t="n">
-        <v>78643</v>
+        <v>78345</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460706</v>
+        <v>460711</v>
       </c>
       <c r="R5" t="n">
-        <v>6873222</v>
+        <v>6873214</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587355</v>
+        <v>121587377</v>
       </c>
       <c r="B6" t="n">
-        <v>78643</v>
+        <v>78691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
         <v>6873319</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121587377</v>
+        <v>121587612</v>
       </c>
       <c r="B7" t="n">
-        <v>78691</v>
+        <v>78643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460722</v>
+        <v>460706</v>
       </c>
       <c r="R7" t="n">
-        <v>6873319</v>
+        <v>6873222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121587594</v>
+        <v>121587355</v>
       </c>
       <c r="B8" t="n">
-        <v>78345</v>
+        <v>78643</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460711</v>
+        <v>460722</v>
       </c>
       <c r="R8" t="n">
-        <v>6873214</v>
+        <v>6873319</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121333520</v>
+        <v>121333407</v>
       </c>
       <c r="B2" t="n">
         <v>79690</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461096</v>
+        <v>461111</v>
       </c>
       <c r="R2" t="n">
-        <v>6872904</v>
+        <v>6872947</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121333407</v>
+        <v>121333520</v>
       </c>
       <c r="B4" t="n">
         <v>79690</v>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461111</v>
+        <v>461096</v>
       </c>
       <c r="R4" t="n">
-        <v>6872947</v>
+        <v>6872904</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587594</v>
+        <v>121587377</v>
       </c>
       <c r="B5" t="n">
-        <v>78345</v>
+        <v>78691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460711</v>
+        <v>460722</v>
       </c>
       <c r="R5" t="n">
-        <v>6873214</v>
+        <v>6873319</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587377</v>
+        <v>121587594</v>
       </c>
       <c r="B6" t="n">
-        <v>78691</v>
+        <v>78345</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460722</v>
+        <v>460711</v>
       </c>
       <c r="R6" t="n">
-        <v>6873319</v>
+        <v>6873214</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121587612</v>
+        <v>121587355</v>
       </c>
       <c r="B7" t="n">
         <v>78643</v>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460706</v>
+        <v>460722</v>
       </c>
       <c r="R7" t="n">
-        <v>6873222</v>
+        <v>6873319</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121587355</v>
+        <v>121587612</v>
       </c>
       <c r="B8" t="n">
         <v>78643</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460722</v>
+        <v>460706</v>
       </c>
       <c r="R8" t="n">
-        <v>6873319</v>
+        <v>6873222</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121333407</v>
+        <v>121333575</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461111</v>
+        <v>461081</v>
       </c>
       <c r="R2" t="n">
-        <v>6872947</v>
+        <v>6872891</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121333575</v>
+        <v>121333520</v>
       </c>
       <c r="B3" t="n">
-        <v>78345</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461081</v>
+        <v>461096</v>
       </c>
       <c r="R3" t="n">
-        <v>6872891</v>
+        <v>6872904</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121333520</v>
+        <v>121333407</v>
       </c>
       <c r="B4" t="n">
         <v>79690</v>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461096</v>
+        <v>461111</v>
       </c>
       <c r="R4" t="n">
-        <v>6872904</v>
+        <v>6872947</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587377</v>
+        <v>121587612</v>
       </c>
       <c r="B5" t="n">
-        <v>78691</v>
+        <v>78643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460722</v>
+        <v>460706</v>
       </c>
       <c r="R5" t="n">
-        <v>6873319</v>
+        <v>6873222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121587612</v>
+        <v>121587377</v>
       </c>
       <c r="B8" t="n">
-        <v>78643</v>
+        <v>78691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460706</v>
+        <v>460722</v>
       </c>
       <c r="R8" t="n">
-        <v>6873222</v>
+        <v>6873319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121333575</v>
+        <v>121333520</v>
       </c>
       <c r="B2" t="n">
-        <v>78345</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461081</v>
+        <v>461096</v>
       </c>
       <c r="R2" t="n">
-        <v>6872891</v>
+        <v>6872904</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121333520</v>
+        <v>121333407</v>
       </c>
       <c r="B3" t="n">
         <v>79690</v>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461096</v>
+        <v>461111</v>
       </c>
       <c r="R3" t="n">
-        <v>6872904</v>
+        <v>6872947</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121333407</v>
+        <v>121333575</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461111</v>
+        <v>461081</v>
       </c>
       <c r="R4" t="n">
-        <v>6872947</v>
+        <v>6872891</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121333520</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121333407</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>121333575</v>
       </c>
       <c r="B4" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>121587612</v>
       </c>
       <c r="B5" t="n">
-        <v>78643</v>
+        <v>78650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>121587594</v>
       </c>
       <c r="B6" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>121587355</v>
       </c>
       <c r="B7" t="n">
-        <v>78643</v>
+        <v>78650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>121587377</v>
       </c>
       <c r="B8" t="n">
-        <v>78691</v>
+        <v>78698</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587377</v>
+        <v>121587594</v>
       </c>
       <c r="B5" t="n">
-        <v>78698</v>
+        <v>78352</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460722</v>
+        <v>460711</v>
       </c>
       <c r="R5" t="n">
-        <v>6873319</v>
+        <v>6873214</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587612</v>
+        <v>121587377</v>
       </c>
       <c r="B6" t="n">
-        <v>78650</v>
+        <v>78698</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460706</v>
+        <v>460722</v>
       </c>
       <c r="R6" t="n">
-        <v>6873222</v>
+        <v>6873319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121587594</v>
+        <v>121587355</v>
       </c>
       <c r="B7" t="n">
-        <v>78352</v>
+        <v>78650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460711</v>
+        <v>460722</v>
       </c>
       <c r="R7" t="n">
-        <v>6873214</v>
+        <v>6873319</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121587355</v>
+        <v>121587612</v>
       </c>
       <c r="B8" t="n">
         <v>78650</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460722</v>
+        <v>460706</v>
       </c>
       <c r="R8" t="n">
-        <v>6873319</v>
+        <v>6873222</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587594</v>
+        <v>121587377</v>
       </c>
       <c r="B5" t="n">
-        <v>78352</v>
+        <v>78698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460711</v>
+        <v>460722</v>
       </c>
       <c r="R5" t="n">
-        <v>6873214</v>
+        <v>6873319</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587377</v>
+        <v>121587594</v>
       </c>
       <c r="B6" t="n">
-        <v>78698</v>
+        <v>78352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460722</v>
+        <v>460711</v>
       </c>
       <c r="R6" t="n">
-        <v>6873319</v>
+        <v>6873214</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121587355</v>
+        <v>121587612</v>
       </c>
       <c r="B7" t="n">
         <v>78650</v>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460722</v>
+        <v>460706</v>
       </c>
       <c r="R7" t="n">
-        <v>6873319</v>
+        <v>6873222</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121587612</v>
+        <v>121587355</v>
       </c>
       <c r="B8" t="n">
         <v>78650</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460706</v>
+        <v>460722</v>
       </c>
       <c r="R8" t="n">
-        <v>6873222</v>
+        <v>6873319</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587377</v>
+        <v>121587612</v>
       </c>
       <c r="B5" t="n">
-        <v>78698</v>
+        <v>78650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460722</v>
+        <v>460706</v>
       </c>
       <c r="R5" t="n">
-        <v>6873319</v>
+        <v>6873222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587594</v>
+        <v>121587355</v>
       </c>
       <c r="B6" t="n">
-        <v>78352</v>
+        <v>78650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460711</v>
+        <v>460722</v>
       </c>
       <c r="R6" t="n">
-        <v>6873214</v>
+        <v>6873319</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121587612</v>
+        <v>121587377</v>
       </c>
       <c r="B7" t="n">
-        <v>78650</v>
+        <v>78698</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460706</v>
+        <v>460722</v>
       </c>
       <c r="R7" t="n">
-        <v>6873222</v>
+        <v>6873319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121587355</v>
+        <v>121587594</v>
       </c>
       <c r="B8" t="n">
-        <v>78650</v>
+        <v>78352</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460722</v>
+        <v>460711</v>
       </c>
       <c r="R8" t="n">
-        <v>6873319</v>
+        <v>6873214</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587612</v>
+        <v>121587355</v>
       </c>
       <c r="B5" t="n">
         <v>78650</v>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460706</v>
+        <v>460722</v>
       </c>
       <c r="R5" t="n">
-        <v>6873222</v>
+        <v>6873319</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587355</v>
+        <v>121587377</v>
       </c>
       <c r="B6" t="n">
-        <v>78650</v>
+        <v>78698</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
         <v>6873319</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121587377</v>
+        <v>121587612</v>
       </c>
       <c r="B7" t="n">
-        <v>78698</v>
+        <v>78650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460722</v>
+        <v>460706</v>
       </c>
       <c r="R7" t="n">
-        <v>6873319</v>
+        <v>6873222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587355</v>
+        <v>121587377</v>
       </c>
       <c r="B5" t="n">
-        <v>78650</v>
+        <v>78698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
         <v>6873319</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587377</v>
+        <v>121587594</v>
       </c>
       <c r="B6" t="n">
-        <v>78698</v>
+        <v>78352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460722</v>
+        <v>460711</v>
       </c>
       <c r="R6" t="n">
-        <v>6873319</v>
+        <v>6873214</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121587594</v>
+        <v>121587355</v>
       </c>
       <c r="B8" t="n">
-        <v>78352</v>
+        <v>78650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460711</v>
+        <v>460722</v>
       </c>
       <c r="R8" t="n">
-        <v>6873214</v>
+        <v>6873319</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587377</v>
+        <v>121587355</v>
       </c>
       <c r="B5" t="n">
-        <v>78698</v>
+        <v>78650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
         <v>6873319</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587594</v>
+        <v>121587377</v>
       </c>
       <c r="B6" t="n">
-        <v>78352</v>
+        <v>78698</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460711</v>
+        <v>460722</v>
       </c>
       <c r="R6" t="n">
-        <v>6873214</v>
+        <v>6873319</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121587612</v>
+        <v>121587594</v>
       </c>
       <c r="B7" t="n">
-        <v>78650</v>
+        <v>78352</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460706</v>
+        <v>460711</v>
       </c>
       <c r="R7" t="n">
-        <v>6873222</v>
+        <v>6873214</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121587355</v>
+        <v>121587612</v>
       </c>
       <c r="B8" t="n">
         <v>78650</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460722</v>
+        <v>460706</v>
       </c>
       <c r="R8" t="n">
-        <v>6873319</v>
+        <v>6873222</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587355</v>
+        <v>121587377</v>
       </c>
       <c r="B5" t="n">
-        <v>78650</v>
+        <v>78711</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
         <v>6873319</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587377</v>
+        <v>121587355</v>
       </c>
       <c r="B6" t="n">
-        <v>78698</v>
+        <v>78663</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
         <v>6873319</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>121587594</v>
       </c>
       <c r="B7" t="n">
-        <v>78352</v>
+        <v>78365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>121587612</v>
       </c>
       <c r="B8" t="n">
-        <v>78650</v>
+        <v>78663</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,6 +1392,1005 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123725467</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>460583</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6873497</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123726535</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>460596</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6873386</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123728023</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>460507</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6873398</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123725365</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>460570</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6873478</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123728124</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>460506</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6873405</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123724854</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>460566</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6873509</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123725130</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>460567</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6873501</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123726451</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>460627</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6873378</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123728236</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>460536</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6873468</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -2393,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123972924</v>
+        <v>123972942</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,50 +2405,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460753</v>
+        <v>460773</v>
       </c>
       <c r="R18" t="n">
-        <v>6872934</v>
+        <v>6872915</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2504,7 +2495,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123970513</v>
+        <v>123972218</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2539,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2553,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461128</v>
+        <v>460794</v>
       </c>
       <c r="R19" t="n">
-        <v>6872930</v>
+        <v>6872877</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2615,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123970610</v>
+        <v>123970875</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2650,7 +2641,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2664,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461109</v>
+        <v>461120</v>
       </c>
       <c r="R20" t="n">
-        <v>6872931</v>
+        <v>6872882</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2726,7 +2717,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123969532</v>
+        <v>123972041</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2761,7 +2752,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2775,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461139</v>
+        <v>460743</v>
       </c>
       <c r="R21" t="n">
-        <v>6873011</v>
+        <v>6872768</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2837,7 +2828,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123970952</v>
+        <v>123970349</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2872,7 +2863,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2886,13 +2877,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461073</v>
+        <v>461128</v>
       </c>
       <c r="R22" t="n">
-        <v>6872885</v>
+        <v>6872966</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2948,7 +2939,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123968641</v>
+        <v>123973080</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2983,7 +2974,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2997,10 +2988,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461153</v>
+        <v>460847</v>
       </c>
       <c r="R23" t="n">
-        <v>6873049</v>
+        <v>6872983</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3059,7 +3050,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123970349</v>
+        <v>123969532</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3094,7 +3085,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3108,13 +3099,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461128</v>
+        <v>461139</v>
       </c>
       <c r="R24" t="n">
-        <v>6872966</v>
+        <v>6873011</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3170,7 +3161,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123973004</v>
+        <v>123969726</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3205,7 +3196,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3219,13 +3210,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460809</v>
+        <v>461123</v>
       </c>
       <c r="R25" t="n">
-        <v>6872950</v>
+        <v>6872994</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3281,7 +3272,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123973080</v>
+        <v>123969327</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3316,7 +3307,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3330,13 +3321,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460847</v>
+        <v>461130</v>
       </c>
       <c r="R26" t="n">
-        <v>6872983</v>
+        <v>6872999</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3392,7 +3383,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123970979</v>
+        <v>123971703</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3427,7 +3418,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3441,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461072</v>
+        <v>460841</v>
       </c>
       <c r="R27" t="n">
-        <v>6872887</v>
+        <v>6872822</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3503,7 +3494,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123972957</v>
+        <v>123970979</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3538,7 +3529,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3552,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460773</v>
+        <v>461072</v>
       </c>
       <c r="R28" t="n">
-        <v>6872915</v>
+        <v>6872887</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3614,7 +3605,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123969726</v>
+        <v>123969799</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3649,7 +3640,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3663,13 +3654,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461123</v>
+        <v>461132</v>
       </c>
       <c r="R29" t="n">
-        <v>6872994</v>
+        <v>6872951</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3725,7 +3716,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123972974</v>
+        <v>123969829</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3774,10 +3765,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460794</v>
+        <v>461121</v>
       </c>
       <c r="R30" t="n">
-        <v>6872937</v>
+        <v>6872969</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3836,10 +3827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123972174</v>
+        <v>123970673</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3848,38 +3839,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460835</v>
+        <v>461113</v>
       </c>
       <c r="R31" t="n">
-        <v>6872866</v>
+        <v>6872925</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123971441</v>
+        <v>123969902</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460898</v>
+        <v>461144</v>
       </c>
       <c r="R32" t="n">
-        <v>6872865</v>
+        <v>6872958</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4023,11 +4023,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4054,7 +4049,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123969829</v>
+        <v>123972590</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4089,7 +4084,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4103,10 +4098,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461121</v>
+        <v>460772</v>
       </c>
       <c r="R33" t="n">
-        <v>6872969</v>
+        <v>6872900</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4165,10 +4160,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123972942</v>
+        <v>123970952</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4177,38 +4172,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460773</v>
+        <v>461073</v>
       </c>
       <c r="R34" t="n">
-        <v>6872915</v>
+        <v>6872885</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4267,7 +4271,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123971888</v>
+        <v>123970431</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4316,10 +4320,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460825</v>
+        <v>461110</v>
       </c>
       <c r="R35" t="n">
-        <v>6872838</v>
+        <v>6872966</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4378,7 +4382,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123971590</v>
+        <v>123968641</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4413,7 +4417,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4427,10 +4431,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460875</v>
+        <v>461153</v>
       </c>
       <c r="R36" t="n">
-        <v>6872840</v>
+        <v>6873049</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4489,7 +4493,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123970760</v>
+        <v>123971836</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4524,7 +4528,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4538,10 +4542,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461123</v>
+        <v>460837</v>
       </c>
       <c r="R37" t="n">
-        <v>6872900</v>
+        <v>6872871</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4600,7 +4604,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123971547</v>
+        <v>123970513</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4635,7 +4639,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4649,10 +4653,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460857</v>
+        <v>461128</v>
       </c>
       <c r="R38" t="n">
-        <v>6872836</v>
+        <v>6872930</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4711,7 +4715,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123970875</v>
+        <v>123971547</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4746,7 +4750,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4760,10 +4764,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461120</v>
+        <v>460857</v>
       </c>
       <c r="R39" t="n">
-        <v>6872882</v>
+        <v>6872836</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5044,7 +5048,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123971836</v>
+        <v>123970610</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5079,7 +5083,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5093,10 +5097,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460837</v>
+        <v>461109</v>
       </c>
       <c r="R42" t="n">
-        <v>6872871</v>
+        <v>6872931</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5155,10 +5159,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123968480</v>
+        <v>123972974</v>
       </c>
       <c r="B43" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5167,41 +5171,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461161</v>
+        <v>460794</v>
       </c>
       <c r="R43" t="n">
-        <v>6873068</v>
+        <v>6872937</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5257,7 +5270,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123972041</v>
+        <v>123972957</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5292,7 +5305,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5306,10 +5319,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460743</v>
+        <v>460773</v>
       </c>
       <c r="R44" t="n">
-        <v>6872768</v>
+        <v>6872915</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5368,7 +5381,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123971703</v>
+        <v>123971888</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5403,7 +5416,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5417,10 +5430,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>460841</v>
+        <v>460825</v>
       </c>
       <c r="R45" t="n">
-        <v>6872822</v>
+        <v>6872838</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5479,7 +5492,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123970673</v>
+        <v>123973004</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5514,7 +5527,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5528,10 +5541,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461113</v>
+        <v>460809</v>
       </c>
       <c r="R46" t="n">
-        <v>6872925</v>
+        <v>6872950</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5590,7 +5603,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123972218</v>
+        <v>123970760</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5625,7 +5638,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5639,13 +5652,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460794</v>
+        <v>461123</v>
       </c>
       <c r="R47" t="n">
-        <v>6872877</v>
+        <v>6872900</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5701,7 +5714,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123969902</v>
+        <v>123970830</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5736,7 +5749,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5750,10 +5763,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461144</v>
+        <v>461105</v>
       </c>
       <c r="R48" t="n">
-        <v>6872958</v>
+        <v>6872902</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5812,7 +5825,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123969327</v>
+        <v>123972924</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5847,7 +5860,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5861,10 +5874,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461130</v>
+        <v>460753</v>
       </c>
       <c r="R49" t="n">
-        <v>6872999</v>
+        <v>6872934</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5923,7 +5936,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123972590</v>
+        <v>123971590</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5958,7 +5971,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5972,10 +5985,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>460772</v>
+        <v>460875</v>
       </c>
       <c r="R50" t="n">
-        <v>6872900</v>
+        <v>6872840</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6034,10 +6047,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123969799</v>
+        <v>123972174</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6046,47 +6059,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461132</v>
+        <v>460835</v>
       </c>
       <c r="R51" t="n">
-        <v>6872951</v>
+        <v>6872866</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6145,10 +6149,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123970830</v>
+        <v>123968480</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6157,50 +6161,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461105</v>
+        <v>461161</v>
       </c>
       <c r="R52" t="n">
-        <v>6872902</v>
+        <v>6873068</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6256,7 +6251,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123970431</v>
+        <v>123971441</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6291,7 +6286,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6305,10 +6300,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461110</v>
+        <v>460898</v>
       </c>
       <c r="R53" t="n">
-        <v>6872966</v>
+        <v>6872865</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6341,6 +6336,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6367,10 +6367,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124371705</v>
+        <v>124371658</v>
       </c>
       <c r="B54" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6379,28 +6379,37 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
@@ -6469,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124372101</v>
+        <v>124372157</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6504,7 +6513,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6518,10 +6527,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460917</v>
+        <v>460932</v>
       </c>
       <c r="R55" t="n">
-        <v>6873090</v>
+        <v>6873104</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6580,7 +6589,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372157</v>
+        <v>124372124</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6615,7 +6624,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6629,10 +6638,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460932</v>
+        <v>460923</v>
       </c>
       <c r="R56" t="n">
-        <v>6873104</v>
+        <v>6873105</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6691,7 +6700,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124371364</v>
+        <v>124371241</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6726,7 +6735,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6740,10 +6749,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460923</v>
+        <v>460930</v>
       </c>
       <c r="R57" t="n">
-        <v>6873201</v>
+        <v>6873206</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6802,7 +6811,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124371443</v>
+        <v>124373016</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6837,7 +6846,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6851,10 +6860,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460918</v>
+        <v>461036</v>
       </c>
       <c r="R58" t="n">
-        <v>6873190</v>
+        <v>6873063</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6913,7 +6922,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372344</v>
+        <v>124371443</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6948,7 +6957,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6962,10 +6971,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460971</v>
+        <v>460918</v>
       </c>
       <c r="R59" t="n">
-        <v>6873061</v>
+        <v>6873190</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7024,7 +7033,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124371984</v>
+        <v>124372853</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7059,7 +7068,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7073,10 +7082,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460918</v>
+        <v>461025</v>
       </c>
       <c r="R60" t="n">
-        <v>6873097</v>
+        <v>6873087</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7246,7 +7255,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372853</v>
+        <v>124372101</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7290,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7304,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461025</v>
+        <v>460917</v>
       </c>
       <c r="R62" t="n">
-        <v>6873087</v>
+        <v>6873090</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7366,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124371658</v>
+        <v>124371956</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7401,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7415,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460910</v>
+        <v>460916</v>
       </c>
       <c r="R63" t="n">
-        <v>6873163</v>
+        <v>6873108</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,7 +7477,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124373016</v>
+        <v>124372344</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7503,7 +7512,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7517,10 +7526,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461036</v>
+        <v>460971</v>
       </c>
       <c r="R64" t="n">
-        <v>6873063</v>
+        <v>6873061</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7588,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124371241</v>
+        <v>124371984</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7614,7 +7623,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7637,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460930</v>
+        <v>460918</v>
       </c>
       <c r="R65" t="n">
-        <v>6873206</v>
+        <v>6873097</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,10 +7699,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372124</v>
+        <v>124371705</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7702,47 +7711,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460923</v>
+        <v>460910</v>
       </c>
       <c r="R66" t="n">
-        <v>6873105</v>
+        <v>6873163</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124371956</v>
+        <v>124371364</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460916</v>
+        <v>460923</v>
       </c>
       <c r="R67" t="n">
-        <v>6873108</v>
+        <v>6873201</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -2393,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123972942</v>
+        <v>123970979</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,38 +2405,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460773</v>
+        <v>461072</v>
       </c>
       <c r="R18" t="n">
-        <v>6872915</v>
+        <v>6872887</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2495,7 +2504,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123972218</v>
+        <v>123969829</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2539,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2544,13 +2553,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460794</v>
+        <v>461121</v>
       </c>
       <c r="R19" t="n">
-        <v>6872877</v>
+        <v>6872969</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2606,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123970875</v>
+        <v>123973080</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2641,7 +2650,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2655,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461120</v>
+        <v>460847</v>
       </c>
       <c r="R20" t="n">
-        <v>6872882</v>
+        <v>6872983</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2717,7 +2726,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123972041</v>
+        <v>123973004</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2752,7 +2761,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2766,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460743</v>
+        <v>460809</v>
       </c>
       <c r="R21" t="n">
-        <v>6872768</v>
+        <v>6872950</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2939,7 +2948,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123973080</v>
+        <v>123970513</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2988,10 +2997,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460847</v>
+        <v>461128</v>
       </c>
       <c r="R23" t="n">
-        <v>6872983</v>
+        <v>6872930</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3050,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123969532</v>
+        <v>123972193</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3085,7 +3094,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3099,13 +3108,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461139</v>
+        <v>460814</v>
       </c>
       <c r="R24" t="n">
-        <v>6873011</v>
+        <v>6872895</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3161,10 +3170,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123969726</v>
+        <v>123972174</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,50 +3182,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461123</v>
+        <v>460835</v>
       </c>
       <c r="R25" t="n">
-        <v>6872994</v>
+        <v>6872866</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123969327</v>
+        <v>123971590</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461130</v>
+        <v>460875</v>
       </c>
       <c r="R26" t="n">
-        <v>6872999</v>
+        <v>6872840</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123971703</v>
+        <v>123970952</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460841</v>
+        <v>461073</v>
       </c>
       <c r="R27" t="n">
-        <v>6872822</v>
+        <v>6872885</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123970979</v>
+        <v>123971703</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461072</v>
+        <v>460841</v>
       </c>
       <c r="R28" t="n">
-        <v>6872887</v>
+        <v>6872822</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123969799</v>
+        <v>123971888</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461132</v>
+        <v>460825</v>
       </c>
       <c r="R29" t="n">
-        <v>6872951</v>
+        <v>6872838</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3716,7 +3716,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123969829</v>
+        <v>123969902</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461121</v>
+        <v>461144</v>
       </c>
       <c r="R30" t="n">
-        <v>6872969</v>
+        <v>6872958</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123970673</v>
+        <v>123968480</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3839,50 +3839,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461113</v>
+        <v>461161</v>
       </c>
       <c r="R31" t="n">
-        <v>6872925</v>
+        <v>6873068</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3938,7 +3929,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123969902</v>
+        <v>123972041</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3973,7 +3964,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3987,10 +3978,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461144</v>
+        <v>460743</v>
       </c>
       <c r="R32" t="n">
-        <v>6872958</v>
+        <v>6872768</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4049,10 +4040,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123972590</v>
+        <v>123972942</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4061,47 +4052,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460772</v>
+        <v>460773</v>
       </c>
       <c r="R33" t="n">
-        <v>6872900</v>
+        <v>6872915</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4160,7 +4142,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123970952</v>
+        <v>123969799</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4195,7 +4177,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4209,10 +4191,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461073</v>
+        <v>461132</v>
       </c>
       <c r="R34" t="n">
-        <v>6872885</v>
+        <v>6872951</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4271,7 +4253,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123970431</v>
+        <v>123970673</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4306,7 +4288,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4320,10 +4302,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461110</v>
+        <v>461113</v>
       </c>
       <c r="R35" t="n">
-        <v>6872966</v>
+        <v>6872925</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4382,7 +4364,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123968641</v>
+        <v>123971547</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4417,7 +4399,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4431,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461153</v>
+        <v>460857</v>
       </c>
       <c r="R36" t="n">
-        <v>6873049</v>
+        <v>6872836</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4493,7 +4475,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123971836</v>
+        <v>123970610</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4528,7 +4510,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4542,10 +4524,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460837</v>
+        <v>461109</v>
       </c>
       <c r="R37" t="n">
-        <v>6872871</v>
+        <v>6872931</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4604,7 +4586,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123970513</v>
+        <v>123969726</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4639,7 +4621,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4653,13 +4635,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461128</v>
+        <v>461123</v>
       </c>
       <c r="R38" t="n">
-        <v>6872930</v>
+        <v>6872994</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4715,7 +4697,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123971547</v>
+        <v>123972957</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4750,7 +4732,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4764,10 +4746,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460857</v>
+        <v>460773</v>
       </c>
       <c r="R39" t="n">
-        <v>6872836</v>
+        <v>6872915</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4826,7 +4808,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123969194</v>
+        <v>123968641</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4861,7 +4843,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4875,10 +4857,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461139</v>
+        <v>461153</v>
       </c>
       <c r="R40" t="n">
-        <v>6872988</v>
+        <v>6873049</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4937,7 +4919,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123972193</v>
+        <v>123972974</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4986,13 +4968,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460814</v>
+        <v>460794</v>
       </c>
       <c r="R41" t="n">
-        <v>6872895</v>
+        <v>6872937</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5048,7 +5030,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123970610</v>
+        <v>123970760</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5083,7 +5065,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5097,10 +5079,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461109</v>
+        <v>461123</v>
       </c>
       <c r="R42" t="n">
-        <v>6872931</v>
+        <v>6872900</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5159,7 +5141,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123972974</v>
+        <v>123970875</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5194,7 +5176,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5208,10 +5190,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460794</v>
+        <v>461120</v>
       </c>
       <c r="R43" t="n">
-        <v>6872937</v>
+        <v>6872882</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5270,7 +5252,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123972957</v>
+        <v>123970830</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5305,7 +5287,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5319,10 +5301,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460773</v>
+        <v>461105</v>
       </c>
       <c r="R44" t="n">
-        <v>6872915</v>
+        <v>6872902</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5381,7 +5363,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123971888</v>
+        <v>123969194</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5416,7 +5398,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5430,10 +5412,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>460825</v>
+        <v>461139</v>
       </c>
       <c r="R45" t="n">
-        <v>6872838</v>
+        <v>6872988</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5492,7 +5474,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123973004</v>
+        <v>123972218</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5527,7 +5509,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5541,13 +5523,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460809</v>
+        <v>460794</v>
       </c>
       <c r="R46" t="n">
-        <v>6872950</v>
+        <v>6872877</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5603,7 +5585,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123970760</v>
+        <v>123969327</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5638,7 +5620,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5652,13 +5634,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461123</v>
+        <v>461130</v>
       </c>
       <c r="R47" t="n">
-        <v>6872900</v>
+        <v>6872999</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5714,7 +5696,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123970830</v>
+        <v>123972924</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5749,7 +5731,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5763,13 +5745,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461105</v>
+        <v>460753</v>
       </c>
       <c r="R48" t="n">
-        <v>6872902</v>
+        <v>6872934</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5825,7 +5807,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123972924</v>
+        <v>123969532</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5860,7 +5842,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5874,13 +5856,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460753</v>
+        <v>461139</v>
       </c>
       <c r="R49" t="n">
-        <v>6872934</v>
+        <v>6873011</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5936,7 +5918,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123971590</v>
+        <v>123971836</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5971,7 +5953,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5985,10 +5967,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>460875</v>
+        <v>460837</v>
       </c>
       <c r="R50" t="n">
-        <v>6872840</v>
+        <v>6872871</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6047,10 +6029,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123972174</v>
+        <v>123971441</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6059,38 +6041,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460835</v>
+        <v>460898</v>
       </c>
       <c r="R51" t="n">
-        <v>6872866</v>
+        <v>6872865</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6123,6 +6114,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6149,10 +6145,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123968480</v>
+        <v>123972590</v>
       </c>
       <c r="B52" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6161,41 +6157,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461161</v>
+        <v>460772</v>
       </c>
       <c r="R52" t="n">
-        <v>6873068</v>
+        <v>6872900</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6251,7 +6256,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123971441</v>
+        <v>123970431</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6286,7 +6291,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6300,10 +6305,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460898</v>
+        <v>461110</v>
       </c>
       <c r="R53" t="n">
-        <v>6872865</v>
+        <v>6872966</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6336,11 +6341,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124371658</v>
+        <v>124371956</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460910</v>
+        <v>460916</v>
       </c>
       <c r="R54" t="n">
-        <v>6873163</v>
+        <v>6873108</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124372157</v>
+        <v>124371364</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460932</v>
+        <v>460923</v>
       </c>
       <c r="R55" t="n">
-        <v>6873104</v>
+        <v>6873201</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372124</v>
+        <v>124372853</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6638,10 +6638,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460923</v>
+        <v>461025</v>
       </c>
       <c r="R56" t="n">
-        <v>6873105</v>
+        <v>6873087</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6700,7 +6700,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124371241</v>
+        <v>124371443</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460930</v>
+        <v>460918</v>
       </c>
       <c r="R57" t="n">
-        <v>6873206</v>
+        <v>6873190</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124373016</v>
+        <v>124372101</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461036</v>
+        <v>460917</v>
       </c>
       <c r="R58" t="n">
-        <v>6873063</v>
+        <v>6873090</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6922,10 +6922,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124371443</v>
+        <v>124371705</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6934,47 +6934,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460918</v>
+        <v>460910</v>
       </c>
       <c r="R59" t="n">
-        <v>6873190</v>
+        <v>6873163</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7033,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372853</v>
+        <v>124371186</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7068,7 +7059,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7082,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461025</v>
+        <v>460943</v>
       </c>
       <c r="R60" t="n">
-        <v>6873087</v>
+        <v>6873209</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7144,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124371186</v>
+        <v>124371658</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7179,7 +7170,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7193,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460943</v>
+        <v>460910</v>
       </c>
       <c r="R61" t="n">
-        <v>6873209</v>
+        <v>6873163</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7255,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372101</v>
+        <v>124372124</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7290,7 +7281,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7304,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460917</v>
+        <v>460923</v>
       </c>
       <c r="R62" t="n">
-        <v>6873090</v>
+        <v>6873105</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7366,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124371956</v>
+        <v>124373016</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7415,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460916</v>
+        <v>461036</v>
       </c>
       <c r="R63" t="n">
-        <v>6873108</v>
+        <v>6873063</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7477,7 +7468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372344</v>
+        <v>124371984</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7512,7 +7503,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7526,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460971</v>
+        <v>460918</v>
       </c>
       <c r="R64" t="n">
-        <v>6873061</v>
+        <v>6873097</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7588,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124371984</v>
+        <v>124372157</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7623,7 +7614,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7637,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460918</v>
+        <v>460932</v>
       </c>
       <c r="R65" t="n">
-        <v>6873097</v>
+        <v>6873104</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7699,10 +7690,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371705</v>
+        <v>124372344</v>
       </c>
       <c r="B66" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7711,38 +7702,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460910</v>
+        <v>460971</v>
       </c>
       <c r="R66" t="n">
-        <v>6873163</v>
+        <v>6873061</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124371364</v>
+        <v>124371241</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460923</v>
+        <v>460930</v>
       </c>
       <c r="R67" t="n">
-        <v>6873201</v>
+        <v>6873206</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -2393,7 +2393,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123970979</v>
+        <v>123971441</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461072</v>
+        <v>460898</v>
       </c>
       <c r="R18" t="n">
-        <v>6872887</v>
+        <v>6872865</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2478,6 +2478,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123969829</v>
+        <v>123973004</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2553,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461121</v>
+        <v>460809</v>
       </c>
       <c r="R19" t="n">
-        <v>6872969</v>
+        <v>6872950</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2615,7 +2620,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123973080</v>
+        <v>123971590</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2664,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460847</v>
+        <v>460875</v>
       </c>
       <c r="R20" t="n">
-        <v>6872983</v>
+        <v>6872840</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2726,7 +2731,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123973004</v>
+        <v>123972041</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2761,7 +2766,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460809</v>
+        <v>460743</v>
       </c>
       <c r="R21" t="n">
-        <v>6872950</v>
+        <v>6872768</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2837,7 +2842,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123970349</v>
+        <v>123971547</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2872,7 +2877,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2886,13 +2891,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461128</v>
+        <v>460857</v>
       </c>
       <c r="R22" t="n">
-        <v>6872966</v>
+        <v>6872836</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2948,7 +2953,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123970513</v>
+        <v>123972957</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2983,7 +2988,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2997,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461128</v>
+        <v>460773</v>
       </c>
       <c r="R23" t="n">
-        <v>6872930</v>
+        <v>6872915</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3059,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123972193</v>
+        <v>123973080</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3094,7 +3099,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3108,13 +3113,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460814</v>
+        <v>460847</v>
       </c>
       <c r="R24" t="n">
-        <v>6872895</v>
+        <v>6872983</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3170,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123972174</v>
+        <v>123972924</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3182,41 +3187,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460835</v>
+        <v>460753</v>
       </c>
       <c r="R25" t="n">
-        <v>6872866</v>
+        <v>6872934</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,7 +3286,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123971590</v>
+        <v>123969532</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3307,7 +3321,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3321,10 +3335,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460875</v>
+        <v>461139</v>
       </c>
       <c r="R26" t="n">
-        <v>6872840</v>
+        <v>6873011</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3383,7 +3397,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123970952</v>
+        <v>123971703</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3418,7 +3432,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3432,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461073</v>
+        <v>460841</v>
       </c>
       <c r="R27" t="n">
-        <v>6872885</v>
+        <v>6872822</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3494,7 +3508,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123971703</v>
+        <v>123970349</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3529,7 +3543,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3543,13 +3557,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460841</v>
+        <v>461128</v>
       </c>
       <c r="R28" t="n">
-        <v>6872822</v>
+        <v>6872966</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3605,7 +3619,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123971888</v>
+        <v>123970979</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3640,7 +3654,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3654,10 +3668,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460825</v>
+        <v>461072</v>
       </c>
       <c r="R29" t="n">
-        <v>6872838</v>
+        <v>6872887</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3716,7 +3730,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123969902</v>
+        <v>123969799</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3751,7 +3765,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3765,10 +3779,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461144</v>
+        <v>461132</v>
       </c>
       <c r="R30" t="n">
-        <v>6872958</v>
+        <v>6872951</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3827,10 +3841,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123968480</v>
+        <v>123970610</v>
       </c>
       <c r="B31" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3839,41 +3853,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461161</v>
+        <v>461109</v>
       </c>
       <c r="R31" t="n">
-        <v>6873068</v>
+        <v>6872931</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3929,7 +3952,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123972041</v>
+        <v>123972974</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3964,7 +3987,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3978,10 +4001,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460743</v>
+        <v>460794</v>
       </c>
       <c r="R32" t="n">
-        <v>6872768</v>
+        <v>6872937</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4040,10 +4063,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123972942</v>
+        <v>123970673</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4052,38 +4075,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460773</v>
+        <v>461113</v>
       </c>
       <c r="R33" t="n">
-        <v>6872915</v>
+        <v>6872925</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4142,7 +4174,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123969799</v>
+        <v>123970513</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4177,7 +4209,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4191,10 +4223,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461132</v>
+        <v>461128</v>
       </c>
       <c r="R34" t="n">
-        <v>6872951</v>
+        <v>6872930</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4253,7 +4285,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123970673</v>
+        <v>123972193</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4288,7 +4320,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4302,13 +4334,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461113</v>
+        <v>460814</v>
       </c>
       <c r="R35" t="n">
-        <v>6872925</v>
+        <v>6872895</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4364,7 +4396,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123971547</v>
+        <v>123968641</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4399,7 +4431,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4413,10 +4445,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460857</v>
+        <v>461153</v>
       </c>
       <c r="R36" t="n">
-        <v>6872836</v>
+        <v>6873049</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4475,7 +4507,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123970610</v>
+        <v>123969194</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4510,7 +4542,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4524,10 +4556,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461109</v>
+        <v>461139</v>
       </c>
       <c r="R37" t="n">
-        <v>6872931</v>
+        <v>6872988</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4586,7 +4618,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123969726</v>
+        <v>123970952</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4635,13 +4667,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461123</v>
+        <v>461073</v>
       </c>
       <c r="R38" t="n">
-        <v>6872994</v>
+        <v>6872885</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4697,10 +4729,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123972957</v>
+        <v>123972174</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4709,47 +4741,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460773</v>
+        <v>460835</v>
       </c>
       <c r="R39" t="n">
-        <v>6872915</v>
+        <v>6872866</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4808,7 +4831,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123968641</v>
+        <v>123971836</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4843,7 +4866,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4857,10 +4880,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461153</v>
+        <v>460837</v>
       </c>
       <c r="R40" t="n">
-        <v>6873049</v>
+        <v>6872871</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4919,7 +4942,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123972974</v>
+        <v>123970875</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4954,7 +4977,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4968,10 +4991,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460794</v>
+        <v>461120</v>
       </c>
       <c r="R41" t="n">
-        <v>6872937</v>
+        <v>6872882</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5030,7 +5053,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123970760</v>
+        <v>123969829</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5065,7 +5088,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5079,10 +5102,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461123</v>
+        <v>461121</v>
       </c>
       <c r="R42" t="n">
-        <v>6872900</v>
+        <v>6872969</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5141,7 +5164,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123970875</v>
+        <v>123972218</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5190,13 +5213,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461120</v>
+        <v>460794</v>
       </c>
       <c r="R43" t="n">
-        <v>6872882</v>
+        <v>6872877</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5252,10 +5275,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123970830</v>
+        <v>123968480</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5264,50 +5287,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461105</v>
+        <v>461161</v>
       </c>
       <c r="R44" t="n">
-        <v>6872902</v>
+        <v>6873068</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5363,7 +5377,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123969194</v>
+        <v>123971888</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5398,7 +5412,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5412,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461139</v>
+        <v>460825</v>
       </c>
       <c r="R45" t="n">
-        <v>6872988</v>
+        <v>6872838</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5474,7 +5488,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123972218</v>
+        <v>123969327</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5509,7 +5523,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5523,10 +5537,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460794</v>
+        <v>461130</v>
       </c>
       <c r="R46" t="n">
-        <v>6872877</v>
+        <v>6872999</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5585,7 +5599,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123969327</v>
+        <v>123969902</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5620,7 +5634,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5634,13 +5648,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461130</v>
+        <v>461144</v>
       </c>
       <c r="R47" t="n">
-        <v>6872999</v>
+        <v>6872958</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5696,7 +5710,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123972924</v>
+        <v>123970830</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5731,7 +5745,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5745,13 +5759,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460753</v>
+        <v>461105</v>
       </c>
       <c r="R48" t="n">
-        <v>6872934</v>
+        <v>6872902</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5807,7 +5821,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123969532</v>
+        <v>123970760</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5842,7 +5856,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5856,10 +5870,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461139</v>
+        <v>461123</v>
       </c>
       <c r="R49" t="n">
-        <v>6873011</v>
+        <v>6872900</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5918,7 +5932,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123971836</v>
+        <v>123969726</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5953,7 +5967,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5967,13 +5981,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>460837</v>
+        <v>461123</v>
       </c>
       <c r="R50" t="n">
-        <v>6872871</v>
+        <v>6872994</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6029,7 +6043,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123971441</v>
+        <v>123970431</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6064,7 +6078,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6078,10 +6092,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460898</v>
+        <v>461110</v>
       </c>
       <c r="R51" t="n">
-        <v>6872865</v>
+        <v>6872966</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6114,11 +6128,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6145,10 +6154,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123972590</v>
+        <v>123972942</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6157,47 +6166,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460772</v>
+        <v>460773</v>
       </c>
       <c r="R52" t="n">
-        <v>6872900</v>
+        <v>6872915</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123970431</v>
+        <v>123972590</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461110</v>
+        <v>460772</v>
       </c>
       <c r="R53" t="n">
-        <v>6872966</v>
+        <v>6872900</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124371956</v>
+        <v>124371186</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460916</v>
+        <v>460943</v>
       </c>
       <c r="R54" t="n">
-        <v>6873108</v>
+        <v>6873209</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124371364</v>
+        <v>124372344</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460923</v>
+        <v>460971</v>
       </c>
       <c r="R55" t="n">
-        <v>6873201</v>
+        <v>6873061</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6589,10 +6589,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372853</v>
+        <v>124371705</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6601,47 +6601,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461025</v>
+        <v>460910</v>
       </c>
       <c r="R56" t="n">
-        <v>6873087</v>
+        <v>6873163</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6700,7 +6691,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124371443</v>
+        <v>124371241</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6735,7 +6726,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6749,10 +6740,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460918</v>
+        <v>460930</v>
       </c>
       <c r="R57" t="n">
-        <v>6873190</v>
+        <v>6873206</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6811,7 +6802,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372101</v>
+        <v>124371658</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6846,7 +6837,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6860,10 +6851,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460917</v>
+        <v>460910</v>
       </c>
       <c r="R58" t="n">
-        <v>6873090</v>
+        <v>6873163</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6922,10 +6913,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124371705</v>
+        <v>124371984</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6934,38 +6925,47 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460910</v>
+        <v>460918</v>
       </c>
       <c r="R59" t="n">
-        <v>6873163</v>
+        <v>6873097</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124371186</v>
+        <v>124371364</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460943</v>
+        <v>460923</v>
       </c>
       <c r="R60" t="n">
-        <v>6873209</v>
+        <v>6873201</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124371658</v>
+        <v>124373016</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460910</v>
+        <v>461036</v>
       </c>
       <c r="R61" t="n">
-        <v>6873163</v>
+        <v>6873063</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372124</v>
+        <v>124372157</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460923</v>
+        <v>460932</v>
       </c>
       <c r="R62" t="n">
-        <v>6873105</v>
+        <v>6873104</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124373016</v>
+        <v>124372124</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461036</v>
+        <v>460923</v>
       </c>
       <c r="R63" t="n">
-        <v>6873063</v>
+        <v>6873105</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124371984</v>
+        <v>124372853</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460918</v>
+        <v>461025</v>
       </c>
       <c r="R64" t="n">
-        <v>6873097</v>
+        <v>6873087</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372157</v>
+        <v>124372101</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460932</v>
+        <v>460917</v>
       </c>
       <c r="R65" t="n">
-        <v>6873104</v>
+        <v>6873090</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372344</v>
+        <v>124371443</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460971</v>
+        <v>460918</v>
       </c>
       <c r="R66" t="n">
-        <v>6873061</v>
+        <v>6873190</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124371241</v>
+        <v>124371956</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460930</v>
+        <v>460916</v>
       </c>
       <c r="R67" t="n">
-        <v>6873206</v>
+        <v>6873108</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -2393,7 +2393,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123971441</v>
+        <v>123970673</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460898</v>
+        <v>461113</v>
       </c>
       <c r="R18" t="n">
-        <v>6872865</v>
+        <v>6872925</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2478,11 +2478,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2504,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123973004</v>
+        <v>123972924</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2544,7 +2539,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2558,13 +2553,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460809</v>
+        <v>460753</v>
       </c>
       <c r="R19" t="n">
-        <v>6872950</v>
+        <v>6872934</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123971590</v>
+        <v>123972942</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2632,47 +2627,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460875</v>
+        <v>460773</v>
       </c>
       <c r="R20" t="n">
-        <v>6872840</v>
+        <v>6872915</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2731,7 +2717,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123972041</v>
+        <v>123969532</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2766,7 +2752,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2780,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460743</v>
+        <v>461139</v>
       </c>
       <c r="R21" t="n">
-        <v>6872768</v>
+        <v>6873011</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2842,7 +2828,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123971547</v>
+        <v>123970830</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2877,7 +2863,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2891,10 +2877,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460857</v>
+        <v>461105</v>
       </c>
       <c r="R22" t="n">
-        <v>6872836</v>
+        <v>6872902</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2953,7 +2939,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123972957</v>
+        <v>123972218</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2988,7 +2974,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3002,13 +2988,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460773</v>
+        <v>460794</v>
       </c>
       <c r="R23" t="n">
-        <v>6872915</v>
+        <v>6872877</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3064,7 +3050,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123973080</v>
+        <v>123972957</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3099,7 +3085,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3113,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460847</v>
+        <v>460773</v>
       </c>
       <c r="R24" t="n">
-        <v>6872983</v>
+        <v>6872915</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3175,7 +3161,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123972924</v>
+        <v>123970349</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3210,7 +3196,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3224,10 +3210,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460753</v>
+        <v>461128</v>
       </c>
       <c r="R25" t="n">
-        <v>6872934</v>
+        <v>6872966</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,7 +3272,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123969532</v>
+        <v>123970513</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3321,7 +3307,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3335,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461139</v>
+        <v>461128</v>
       </c>
       <c r="R26" t="n">
-        <v>6873011</v>
+        <v>6872930</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3397,7 +3383,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123971703</v>
+        <v>123972974</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3432,7 +3418,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3446,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460841</v>
+        <v>460794</v>
       </c>
       <c r="R27" t="n">
-        <v>6872822</v>
+        <v>6872937</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3508,7 +3494,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123970349</v>
+        <v>123969829</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3543,7 +3529,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3557,13 +3543,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461128</v>
+        <v>461121</v>
       </c>
       <c r="R28" t="n">
-        <v>6872966</v>
+        <v>6872969</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,7 +3605,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123970979</v>
+        <v>123973080</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3654,7 +3640,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3668,10 +3654,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461072</v>
+        <v>460847</v>
       </c>
       <c r="R29" t="n">
-        <v>6872887</v>
+        <v>6872983</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3730,7 +3716,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123969799</v>
+        <v>123969902</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3765,7 +3751,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3779,10 +3765,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461132</v>
+        <v>461144</v>
       </c>
       <c r="R30" t="n">
-        <v>6872951</v>
+        <v>6872958</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3841,7 +3827,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123970610</v>
+        <v>123970952</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3876,7 +3862,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3890,10 +3876,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461109</v>
+        <v>461073</v>
       </c>
       <c r="R31" t="n">
-        <v>6872931</v>
+        <v>6872885</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3952,7 +3938,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123972974</v>
+        <v>123969726</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3987,7 +3973,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4001,13 +3987,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460794</v>
+        <v>461123</v>
       </c>
       <c r="R32" t="n">
-        <v>6872937</v>
+        <v>6872994</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4063,7 +4049,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123970673</v>
+        <v>123972193</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4098,7 +4084,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4112,13 +4098,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461113</v>
+        <v>460814</v>
       </c>
       <c r="R33" t="n">
-        <v>6872925</v>
+        <v>6872895</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4174,7 +4160,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123970513</v>
+        <v>123971836</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4209,7 +4195,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4223,10 +4209,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461128</v>
+        <v>460837</v>
       </c>
       <c r="R34" t="n">
-        <v>6872930</v>
+        <v>6872871</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4285,7 +4271,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123972193</v>
+        <v>123969194</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4320,7 +4306,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4334,13 +4320,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460814</v>
+        <v>461139</v>
       </c>
       <c r="R35" t="n">
-        <v>6872895</v>
+        <v>6872988</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4396,7 +4382,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123968641</v>
+        <v>123971547</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4431,7 +4417,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4445,10 +4431,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461153</v>
+        <v>460857</v>
       </c>
       <c r="R36" t="n">
-        <v>6873049</v>
+        <v>6872836</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4507,10 +4493,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123969194</v>
+        <v>123972174</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4519,47 +4505,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461139</v>
+        <v>460835</v>
       </c>
       <c r="R37" t="n">
-        <v>6872988</v>
+        <v>6872866</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4618,7 +4595,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123970952</v>
+        <v>123971703</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4653,7 +4630,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4667,10 +4644,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461073</v>
+        <v>460841</v>
       </c>
       <c r="R38" t="n">
-        <v>6872885</v>
+        <v>6872822</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4729,10 +4706,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123972174</v>
+        <v>123971590</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4741,38 +4718,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460835</v>
+        <v>460875</v>
       </c>
       <c r="R39" t="n">
-        <v>6872866</v>
+        <v>6872840</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4831,7 +4817,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123971836</v>
+        <v>123972590</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4866,7 +4852,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4880,10 +4866,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460837</v>
+        <v>460772</v>
       </c>
       <c r="R40" t="n">
-        <v>6872871</v>
+        <v>6872900</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4942,7 +4928,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123970875</v>
+        <v>123973004</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4977,7 +4963,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4991,10 +4977,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461120</v>
+        <v>460809</v>
       </c>
       <c r="R41" t="n">
-        <v>6872882</v>
+        <v>6872950</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5053,7 +5039,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123969829</v>
+        <v>123969799</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5088,7 +5074,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5102,10 +5088,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461121</v>
+        <v>461132</v>
       </c>
       <c r="R42" t="n">
-        <v>6872969</v>
+        <v>6872951</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5164,7 +5150,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123972218</v>
+        <v>123968641</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5199,7 +5185,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5213,13 +5199,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460794</v>
+        <v>461153</v>
       </c>
       <c r="R43" t="n">
-        <v>6872877</v>
+        <v>6873049</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5275,10 +5261,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123968480</v>
+        <v>123970760</v>
       </c>
       <c r="B44" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5287,41 +5273,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461161</v>
+        <v>461123</v>
       </c>
       <c r="R44" t="n">
-        <v>6873068</v>
+        <v>6872900</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5488,7 +5483,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123969327</v>
+        <v>123972041</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5523,7 +5518,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5537,13 +5532,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461130</v>
+        <v>460743</v>
       </c>
       <c r="R46" t="n">
-        <v>6872999</v>
+        <v>6872768</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5599,7 +5594,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123969902</v>
+        <v>123971441</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461144</v>
+        <v>460898</v>
       </c>
       <c r="R47" t="n">
-        <v>6872958</v>
+        <v>6872865</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5684,6 +5679,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5710,7 +5710,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123970830</v>
+        <v>123970979</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461105</v>
+        <v>461072</v>
       </c>
       <c r="R48" t="n">
-        <v>6872902</v>
+        <v>6872887</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5821,7 +5821,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123970760</v>
+        <v>123970610</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461123</v>
+        <v>461109</v>
       </c>
       <c r="R49" t="n">
-        <v>6872900</v>
+        <v>6872931</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123969726</v>
+        <v>123970431</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5981,13 +5981,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461123</v>
+        <v>461110</v>
       </c>
       <c r="R50" t="n">
-        <v>6872994</v>
+        <v>6872966</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123970431</v>
+        <v>123969327</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6092,13 +6092,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461110</v>
+        <v>461130</v>
       </c>
       <c r="R51" t="n">
-        <v>6872966</v>
+        <v>6872999</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123972942</v>
+        <v>123970875</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6166,38 +6166,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460773</v>
+        <v>461120</v>
       </c>
       <c r="R52" t="n">
-        <v>6872915</v>
+        <v>6872882</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6256,10 +6265,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123972590</v>
+        <v>123968480</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6268,50 +6277,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460772</v>
+        <v>461161</v>
       </c>
       <c r="R53" t="n">
-        <v>6872900</v>
+        <v>6873068</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124371186</v>
+        <v>124372101</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460943</v>
+        <v>460917</v>
       </c>
       <c r="R54" t="n">
-        <v>6873209</v>
+        <v>6873090</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124372344</v>
+        <v>124371658</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460971</v>
+        <v>460910</v>
       </c>
       <c r="R55" t="n">
-        <v>6873061</v>
+        <v>6873163</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6691,7 +6691,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124371241</v>
+        <v>124371186</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460930</v>
+        <v>460943</v>
       </c>
       <c r="R57" t="n">
-        <v>6873206</v>
+        <v>6873209</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124371658</v>
+        <v>124372157</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460910</v>
+        <v>460932</v>
       </c>
       <c r="R58" t="n">
-        <v>6873163</v>
+        <v>6873104</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6913,7 +6913,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124371984</v>
+        <v>124371241</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460918</v>
+        <v>460930</v>
       </c>
       <c r="R59" t="n">
-        <v>6873097</v>
+        <v>6873206</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124371364</v>
+        <v>124371956</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460923</v>
+        <v>460916</v>
       </c>
       <c r="R60" t="n">
-        <v>6873201</v>
+        <v>6873108</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124373016</v>
+        <v>124372124</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461036</v>
+        <v>460923</v>
       </c>
       <c r="R61" t="n">
-        <v>6873063</v>
+        <v>6873105</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372157</v>
+        <v>124372853</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460932</v>
+        <v>461025</v>
       </c>
       <c r="R62" t="n">
-        <v>6873104</v>
+        <v>6873087</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372124</v>
+        <v>124371443</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460923</v>
+        <v>460918</v>
       </c>
       <c r="R63" t="n">
-        <v>6873105</v>
+        <v>6873190</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372853</v>
+        <v>124372344</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461025</v>
+        <v>460971</v>
       </c>
       <c r="R64" t="n">
-        <v>6873087</v>
+        <v>6873061</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372101</v>
+        <v>124371984</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460917</v>
+        <v>460918</v>
       </c>
       <c r="R65" t="n">
-        <v>6873090</v>
+        <v>6873097</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371443</v>
+        <v>124371364</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460918</v>
+        <v>460923</v>
       </c>
       <c r="R66" t="n">
-        <v>6873190</v>
+        <v>6873201</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124371956</v>
+        <v>124373016</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460916</v>
+        <v>461036</v>
       </c>
       <c r="R67" t="n">
-        <v>6873108</v>
+        <v>6873063</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -2393,7 +2393,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123970673</v>
+        <v>123972924</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461113</v>
+        <v>460753</v>
       </c>
       <c r="R18" t="n">
-        <v>6872925</v>
+        <v>6872934</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123972924</v>
+        <v>123969532</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460753</v>
+        <v>461139</v>
       </c>
       <c r="R19" t="n">
-        <v>6872934</v>
+        <v>6873011</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123972942</v>
+        <v>123971703</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,38 +2627,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460773</v>
+        <v>460841</v>
       </c>
       <c r="R20" t="n">
-        <v>6872915</v>
+        <v>6872822</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2717,7 +2726,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123969532</v>
+        <v>123968641</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2752,7 +2761,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2766,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461139</v>
+        <v>461153</v>
       </c>
       <c r="R21" t="n">
-        <v>6873011</v>
+        <v>6873049</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2828,7 +2837,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123970830</v>
+        <v>123971441</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2863,7 +2872,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2877,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461105</v>
+        <v>460898</v>
       </c>
       <c r="R22" t="n">
-        <v>6872902</v>
+        <v>6872865</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2913,6 +2922,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2939,10 +2953,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123972218</v>
+        <v>123972174</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2951,50 +2965,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460794</v>
+        <v>460835</v>
       </c>
       <c r="R23" t="n">
-        <v>6872877</v>
+        <v>6872866</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,7 +3055,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123972957</v>
+        <v>123971547</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3085,7 +3090,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3099,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460773</v>
+        <v>460857</v>
       </c>
       <c r="R24" t="n">
-        <v>6872915</v>
+        <v>6872836</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3161,7 +3166,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123970349</v>
+        <v>123970760</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3196,7 +3201,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3210,13 +3215,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461128</v>
+        <v>461123</v>
       </c>
       <c r="R25" t="n">
-        <v>6872966</v>
+        <v>6872900</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,7 +3277,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123970513</v>
+        <v>123972957</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3307,7 +3312,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3321,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461128</v>
+        <v>460773</v>
       </c>
       <c r="R26" t="n">
-        <v>6872930</v>
+        <v>6872915</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3383,7 +3388,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123972974</v>
+        <v>123970349</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3418,7 +3423,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3432,13 +3437,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460794</v>
+        <v>461128</v>
       </c>
       <c r="R27" t="n">
-        <v>6872937</v>
+        <v>6872966</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3494,7 +3499,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123969829</v>
+        <v>123971888</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3529,7 +3534,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3543,10 +3548,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461121</v>
+        <v>460825</v>
       </c>
       <c r="R28" t="n">
-        <v>6872969</v>
+        <v>6872838</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3605,7 +3610,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123973080</v>
+        <v>123972974</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3640,7 +3645,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3654,10 +3659,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460847</v>
+        <v>460794</v>
       </c>
       <c r="R29" t="n">
-        <v>6872983</v>
+        <v>6872937</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3716,7 +3721,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123969902</v>
+        <v>123970431</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3751,7 +3756,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3765,10 +3770,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461144</v>
+        <v>461110</v>
       </c>
       <c r="R30" t="n">
-        <v>6872958</v>
+        <v>6872966</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3827,7 +3832,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123970952</v>
+        <v>123970830</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3876,10 +3881,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461073</v>
+        <v>461105</v>
       </c>
       <c r="R31" t="n">
-        <v>6872885</v>
+        <v>6872902</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3938,7 +3943,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123969726</v>
+        <v>123970952</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3987,13 +3992,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461123</v>
+        <v>461073</v>
       </c>
       <c r="R32" t="n">
-        <v>6872994</v>
+        <v>6872885</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4049,7 +4054,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123972193</v>
+        <v>123970673</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4084,7 +4089,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4098,13 +4103,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460814</v>
+        <v>461113</v>
       </c>
       <c r="R33" t="n">
-        <v>6872895</v>
+        <v>6872925</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123971836</v>
+        <v>123972218</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4195,7 +4200,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4209,13 +4214,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460837</v>
+        <v>460794</v>
       </c>
       <c r="R34" t="n">
-        <v>6872871</v>
+        <v>6872877</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4271,7 +4276,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123969194</v>
+        <v>123970513</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4306,7 +4311,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4320,10 +4325,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461139</v>
+        <v>461128</v>
       </c>
       <c r="R35" t="n">
-        <v>6872988</v>
+        <v>6872930</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4382,7 +4387,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123971547</v>
+        <v>123971836</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4417,7 +4422,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4431,10 +4436,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460857</v>
+        <v>460837</v>
       </c>
       <c r="R36" t="n">
-        <v>6872836</v>
+        <v>6872871</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4493,10 +4498,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123972174</v>
+        <v>123969902</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4505,38 +4510,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460835</v>
+        <v>461144</v>
       </c>
       <c r="R37" t="n">
-        <v>6872866</v>
+        <v>6872958</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4595,7 +4609,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123971703</v>
+        <v>123970610</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4630,7 +4644,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4644,10 +4658,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460841</v>
+        <v>461109</v>
       </c>
       <c r="R38" t="n">
-        <v>6872822</v>
+        <v>6872931</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4706,7 +4720,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123971590</v>
+        <v>123973080</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4755,10 +4769,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460875</v>
+        <v>460847</v>
       </c>
       <c r="R39" t="n">
-        <v>6872840</v>
+        <v>6872983</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4817,7 +4831,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123972590</v>
+        <v>123969829</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4852,7 +4866,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4866,10 +4880,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460772</v>
+        <v>461121</v>
       </c>
       <c r="R40" t="n">
-        <v>6872900</v>
+        <v>6872969</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4928,7 +4942,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123973004</v>
+        <v>123972193</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4977,13 +4991,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460809</v>
+        <v>460814</v>
       </c>
       <c r="R41" t="n">
-        <v>6872950</v>
+        <v>6872895</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5039,7 +5053,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123969799</v>
+        <v>123971590</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5074,7 +5088,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5088,10 +5102,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461132</v>
+        <v>460875</v>
       </c>
       <c r="R42" t="n">
-        <v>6872951</v>
+        <v>6872840</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5150,10 +5164,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123968641</v>
+        <v>123972942</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5162,47 +5176,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461153</v>
+        <v>460773</v>
       </c>
       <c r="R43" t="n">
-        <v>6873049</v>
+        <v>6872915</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5261,7 +5266,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123970760</v>
+        <v>123973004</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5296,7 +5301,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5310,10 +5315,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461123</v>
+        <v>460809</v>
       </c>
       <c r="R44" t="n">
-        <v>6872900</v>
+        <v>6872950</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5372,10 +5377,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123971888</v>
+        <v>123968480</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5384,50 +5389,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>460825</v>
+        <v>461161</v>
       </c>
       <c r="R45" t="n">
-        <v>6872838</v>
+        <v>6873068</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5483,7 +5479,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123972041</v>
+        <v>123969327</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5518,7 +5514,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5532,13 +5528,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460743</v>
+        <v>461130</v>
       </c>
       <c r="R46" t="n">
-        <v>6872768</v>
+        <v>6872999</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5594,7 +5590,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123971441</v>
+        <v>123970979</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5629,7 +5625,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5643,10 +5639,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460898</v>
+        <v>461072</v>
       </c>
       <c r="R47" t="n">
-        <v>6872865</v>
+        <v>6872887</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5679,11 +5675,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5710,7 +5701,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123970979</v>
+        <v>123972590</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5745,7 +5736,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5759,10 +5750,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461072</v>
+        <v>460772</v>
       </c>
       <c r="R48" t="n">
-        <v>6872887</v>
+        <v>6872900</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5821,7 +5812,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123970610</v>
+        <v>123970875</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5856,7 +5847,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5870,10 +5861,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461109</v>
+        <v>461120</v>
       </c>
       <c r="R49" t="n">
-        <v>6872931</v>
+        <v>6872882</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5932,7 +5923,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123970431</v>
+        <v>123969194</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5967,7 +5958,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5981,10 +5972,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461110</v>
+        <v>461139</v>
       </c>
       <c r="R50" t="n">
-        <v>6872966</v>
+        <v>6872988</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6043,7 +6034,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123969327</v>
+        <v>123969726</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6078,7 +6069,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6092,10 +6083,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461130</v>
+        <v>461123</v>
       </c>
       <c r="R51" t="n">
-        <v>6872999</v>
+        <v>6872994</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6154,7 +6145,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123970875</v>
+        <v>123969799</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -6189,7 +6180,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6203,10 +6194,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461120</v>
+        <v>461132</v>
       </c>
       <c r="R52" t="n">
-        <v>6872882</v>
+        <v>6872951</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6265,10 +6256,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123968480</v>
+        <v>123972041</v>
       </c>
       <c r="B53" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6277,41 +6268,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461161</v>
+        <v>460743</v>
       </c>
       <c r="R53" t="n">
-        <v>6873068</v>
+        <v>6872768</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124372101</v>
+        <v>124371984</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460917</v>
+        <v>460918</v>
       </c>
       <c r="R54" t="n">
-        <v>6873090</v>
+        <v>6873097</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124371658</v>
+        <v>124371705</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6490,37 +6490,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
@@ -6589,10 +6580,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124371705</v>
+        <v>124371658</v>
       </c>
       <c r="B56" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6601,28 +6592,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
@@ -6691,7 +6691,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124371186</v>
+        <v>124372124</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460943</v>
+        <v>460923</v>
       </c>
       <c r="R57" t="n">
-        <v>6873209</v>
+        <v>6873105</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372157</v>
+        <v>124372101</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460932</v>
+        <v>460917</v>
       </c>
       <c r="R58" t="n">
-        <v>6873104</v>
+        <v>6873090</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124371956</v>
+        <v>124372853</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460916</v>
+        <v>461025</v>
       </c>
       <c r="R60" t="n">
-        <v>6873108</v>
+        <v>6873087</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372124</v>
+        <v>124372157</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460923</v>
+        <v>460932</v>
       </c>
       <c r="R61" t="n">
-        <v>6873105</v>
+        <v>6873104</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372853</v>
+        <v>124371443</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461025</v>
+        <v>460918</v>
       </c>
       <c r="R62" t="n">
-        <v>6873087</v>
+        <v>6873190</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124371443</v>
+        <v>124371364</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460918</v>
+        <v>460923</v>
       </c>
       <c r="R63" t="n">
-        <v>6873190</v>
+        <v>6873201</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124371984</v>
+        <v>124371186</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460918</v>
+        <v>460943</v>
       </c>
       <c r="R65" t="n">
-        <v>6873097</v>
+        <v>6873209</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371364</v>
+        <v>124371956</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460923</v>
+        <v>460916</v>
       </c>
       <c r="R66" t="n">
-        <v>6873201</v>
+        <v>6873108</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -3388,7 +3388,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123970349</v>
+        <v>123971888</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3437,13 +3437,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461128</v>
+        <v>460825</v>
       </c>
       <c r="R27" t="n">
-        <v>6872966</v>
+        <v>6872838</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123971888</v>
+        <v>123970349</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460825</v>
+        <v>461128</v>
       </c>
       <c r="R28" t="n">
-        <v>6872838</v>
+        <v>6872966</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123970610</v>
+        <v>123973080</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461109</v>
+        <v>460847</v>
       </c>
       <c r="R38" t="n">
-        <v>6872931</v>
+        <v>6872983</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4720,7 +4720,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123973080</v>
+        <v>123969829</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460847</v>
+        <v>461121</v>
       </c>
       <c r="R39" t="n">
-        <v>6872983</v>
+        <v>6872969</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4831,7 +4831,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123969829</v>
+        <v>123972193</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4880,13 +4880,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461121</v>
+        <v>460814</v>
       </c>
       <c r="R40" t="n">
-        <v>6872969</v>
+        <v>6872895</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123972193</v>
+        <v>123970610</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4991,13 +4991,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460814</v>
+        <v>461109</v>
       </c>
       <c r="R41" t="n">
-        <v>6872895</v>
+        <v>6872931</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123970875</v>
+        <v>123969194</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461120</v>
+        <v>461139</v>
       </c>
       <c r="R49" t="n">
-        <v>6872882</v>
+        <v>6872988</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5923,7 +5923,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123969194</v>
+        <v>123970875</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461139</v>
+        <v>461120</v>
       </c>
       <c r="R50" t="n">
-        <v>6872988</v>
+        <v>6872882</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124371984</v>
+        <v>124371658</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460918</v>
+        <v>460910</v>
       </c>
       <c r="R54" t="n">
-        <v>6873097</v>
+        <v>6873163</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124371705</v>
+        <v>124371984</v>
       </c>
       <c r="B55" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6490,38 +6490,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460910</v>
+        <v>460918</v>
       </c>
       <c r="R55" t="n">
-        <v>6873163</v>
+        <v>6873097</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6580,7 +6589,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124371658</v>
+        <v>124371364</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6615,7 +6624,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6629,10 +6638,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460910</v>
+        <v>460923</v>
       </c>
       <c r="R56" t="n">
-        <v>6873163</v>
+        <v>6873201</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6691,7 +6700,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372124</v>
+        <v>124372853</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6726,7 +6735,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6740,10 +6749,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460923</v>
+        <v>461025</v>
       </c>
       <c r="R57" t="n">
-        <v>6873105</v>
+        <v>6873087</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6802,7 +6811,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372101</v>
+        <v>124372157</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6837,7 +6846,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6851,10 +6860,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460917</v>
+        <v>460932</v>
       </c>
       <c r="R58" t="n">
-        <v>6873090</v>
+        <v>6873104</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7024,7 +7033,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372853</v>
+        <v>124371956</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7059,7 +7068,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7073,10 +7082,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461025</v>
+        <v>460916</v>
       </c>
       <c r="R60" t="n">
-        <v>6873087</v>
+        <v>6873108</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7144,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372157</v>
+        <v>124371186</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7170,7 +7179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7184,10 +7193,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460932</v>
+        <v>460943</v>
       </c>
       <c r="R61" t="n">
-        <v>6873104</v>
+        <v>6873209</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7255,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124371443</v>
+        <v>124372101</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7290,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7304,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460918</v>
+        <v>460917</v>
       </c>
       <c r="R62" t="n">
-        <v>6873190</v>
+        <v>6873090</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7366,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124371364</v>
+        <v>124371443</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7401,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7415,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460923</v>
+        <v>460918</v>
       </c>
       <c r="R63" t="n">
-        <v>6873201</v>
+        <v>6873190</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,10 +7477,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372344</v>
+        <v>124371705</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7480,47 +7489,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460971</v>
+        <v>460910</v>
       </c>
       <c r="R64" t="n">
-        <v>6873061</v>
+        <v>6873163</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124371186</v>
+        <v>124372344</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460943</v>
+        <v>460971</v>
       </c>
       <c r="R65" t="n">
-        <v>6873209</v>
+        <v>6873061</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371956</v>
+        <v>124373016</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460916</v>
+        <v>461036</v>
       </c>
       <c r="R66" t="n">
-        <v>6873108</v>
+        <v>6873063</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124373016</v>
+        <v>124372124</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461036</v>
+        <v>460923</v>
       </c>
       <c r="R67" t="n">
-        <v>6873063</v>
+        <v>6873105</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124371658</v>
+        <v>124372124</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460910</v>
+        <v>460923</v>
       </c>
       <c r="R54" t="n">
-        <v>6873163</v>
+        <v>6873105</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124371984</v>
+        <v>124371364</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460918</v>
+        <v>460923</v>
       </c>
       <c r="R55" t="n">
-        <v>6873097</v>
+        <v>6873201</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124371364</v>
+        <v>124371241</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6638,10 +6638,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460923</v>
+        <v>460930</v>
       </c>
       <c r="R56" t="n">
-        <v>6873201</v>
+        <v>6873206</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6700,10 +6700,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372853</v>
+        <v>124371705</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6712,47 +6712,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461025</v>
+        <v>460910</v>
       </c>
       <c r="R57" t="n">
-        <v>6873087</v>
+        <v>6873163</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6922,7 +6913,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124371241</v>
+        <v>124372101</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6957,7 +6948,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6971,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460930</v>
+        <v>460917</v>
       </c>
       <c r="R59" t="n">
-        <v>6873206</v>
+        <v>6873090</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7033,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124371956</v>
+        <v>124371984</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7082,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460916</v>
+        <v>460918</v>
       </c>
       <c r="R60" t="n">
-        <v>6873108</v>
+        <v>6873097</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7144,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124371186</v>
+        <v>124371658</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7179,7 +7170,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7193,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460943</v>
+        <v>460910</v>
       </c>
       <c r="R61" t="n">
-        <v>6873209</v>
+        <v>6873163</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7255,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372101</v>
+        <v>124373016</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7304,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460917</v>
+        <v>461036</v>
       </c>
       <c r="R62" t="n">
-        <v>6873090</v>
+        <v>6873063</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7366,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124371443</v>
+        <v>124371186</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7401,7 +7392,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7415,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460918</v>
+        <v>460943</v>
       </c>
       <c r="R63" t="n">
-        <v>6873190</v>
+        <v>6873209</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7477,10 +7468,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124371705</v>
+        <v>124372853</v>
       </c>
       <c r="B64" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7489,38 +7480,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460910</v>
+        <v>461025</v>
       </c>
       <c r="R64" t="n">
-        <v>6873163</v>
+        <v>6873087</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124373016</v>
+        <v>124371956</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461036</v>
+        <v>460916</v>
       </c>
       <c r="R66" t="n">
-        <v>6873063</v>
+        <v>6873108</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372124</v>
+        <v>124371443</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460923</v>
+        <v>460918</v>
       </c>
       <c r="R67" t="n">
-        <v>6873105</v>
+        <v>6873190</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371956</v>
+        <v>124371443</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460916</v>
+        <v>460918</v>
       </c>
       <c r="R66" t="n">
-        <v>6873108</v>
+        <v>6873190</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124371443</v>
+        <v>124371956</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460918</v>
+        <v>460916</v>
       </c>
       <c r="R67" t="n">
-        <v>6873190</v>
+        <v>6873108</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124372124</v>
+        <v>124372853</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460923</v>
+        <v>461025</v>
       </c>
       <c r="R54" t="n">
-        <v>6873105</v>
+        <v>6873087</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124371364</v>
+        <v>124372344</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460923</v>
+        <v>460971</v>
       </c>
       <c r="R55" t="n">
-        <v>6873201</v>
+        <v>6873061</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124371241</v>
+        <v>124371984</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6638,10 +6638,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460930</v>
+        <v>460918</v>
       </c>
       <c r="R56" t="n">
-        <v>6873206</v>
+        <v>6873097</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6700,10 +6700,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124371705</v>
+        <v>124371186</v>
       </c>
       <c r="B57" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6712,38 +6712,47 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460910</v>
+        <v>460943</v>
       </c>
       <c r="R57" t="n">
-        <v>6873163</v>
+        <v>6873209</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6802,10 +6811,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372157</v>
+        <v>124371705</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6814,47 +6823,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460932</v>
+        <v>460910</v>
       </c>
       <c r="R58" t="n">
-        <v>6873104</v>
+        <v>6873163</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6913,7 +6913,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372101</v>
+        <v>124372157</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460917</v>
+        <v>460932</v>
       </c>
       <c r="R59" t="n">
-        <v>6873090</v>
+        <v>6873104</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124371984</v>
+        <v>124372124</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460918</v>
+        <v>460923</v>
       </c>
       <c r="R60" t="n">
-        <v>6873097</v>
+        <v>6873105</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124371658</v>
+        <v>124371364</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460910</v>
+        <v>460923</v>
       </c>
       <c r="R61" t="n">
-        <v>6873163</v>
+        <v>6873201</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124373016</v>
+        <v>124371658</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461036</v>
+        <v>460910</v>
       </c>
       <c r="R62" t="n">
-        <v>6873063</v>
+        <v>6873163</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124371186</v>
+        <v>124373016</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460943</v>
+        <v>461036</v>
       </c>
       <c r="R63" t="n">
-        <v>6873209</v>
+        <v>6873063</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372853</v>
+        <v>124371241</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461025</v>
+        <v>460930</v>
       </c>
       <c r="R64" t="n">
-        <v>6873087</v>
+        <v>6873206</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372344</v>
+        <v>124372101</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460971</v>
+        <v>460917</v>
       </c>
       <c r="R65" t="n">
-        <v>6873061</v>
+        <v>6873090</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124372853</v>
+        <v>124372124</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461025</v>
+        <v>460923</v>
       </c>
       <c r="R54" t="n">
-        <v>6873087</v>
+        <v>6873105</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124372344</v>
+        <v>124371658</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460971</v>
+        <v>460910</v>
       </c>
       <c r="R55" t="n">
-        <v>6873061</v>
+        <v>6873163</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124371984</v>
+        <v>124372157</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6638,10 +6638,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460918</v>
+        <v>460932</v>
       </c>
       <c r="R56" t="n">
-        <v>6873097</v>
+        <v>6873104</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6700,10 +6700,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124371186</v>
+        <v>124371705</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6712,47 +6712,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460943</v>
+        <v>460910</v>
       </c>
       <c r="R57" t="n">
-        <v>6873209</v>
+        <v>6873163</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6811,10 +6802,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124371705</v>
+        <v>124372101</v>
       </c>
       <c r="B58" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6823,38 +6814,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460910</v>
+        <v>460917</v>
       </c>
       <c r="R58" t="n">
-        <v>6873163</v>
+        <v>6873090</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6913,7 +6913,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372157</v>
+        <v>124372344</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460932</v>
+        <v>460971</v>
       </c>
       <c r="R59" t="n">
-        <v>6873104</v>
+        <v>6873061</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372124</v>
+        <v>124373016</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460923</v>
+        <v>461036</v>
       </c>
       <c r="R60" t="n">
-        <v>6873105</v>
+        <v>6873063</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124371364</v>
+        <v>124371984</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460923</v>
+        <v>460918</v>
       </c>
       <c r="R61" t="n">
-        <v>6873201</v>
+        <v>6873097</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124371658</v>
+        <v>124371956</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460910</v>
+        <v>460916</v>
       </c>
       <c r="R62" t="n">
-        <v>6873163</v>
+        <v>6873108</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124373016</v>
+        <v>124372853</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461036</v>
+        <v>461025</v>
       </c>
       <c r="R63" t="n">
-        <v>6873063</v>
+        <v>6873087</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124371241</v>
+        <v>124371443</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460930</v>
+        <v>460918</v>
       </c>
       <c r="R64" t="n">
-        <v>6873206</v>
+        <v>6873190</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372101</v>
+        <v>124371241</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460917</v>
+        <v>460930</v>
       </c>
       <c r="R65" t="n">
-        <v>6873090</v>
+        <v>6873206</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371443</v>
+        <v>124371364</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460918</v>
+        <v>460923</v>
       </c>
       <c r="R66" t="n">
-        <v>6873190</v>
+        <v>6873201</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124371956</v>
+        <v>124371186</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460916</v>
+        <v>460943</v>
       </c>
       <c r="R67" t="n">
-        <v>6873108</v>
+        <v>6873209</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124372124</v>
+        <v>124373016</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460923</v>
+        <v>461036</v>
       </c>
       <c r="R54" t="n">
-        <v>6873105</v>
+        <v>6873063</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124371658</v>
+        <v>124372157</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460910</v>
+        <v>460932</v>
       </c>
       <c r="R55" t="n">
-        <v>6873163</v>
+        <v>6873104</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372157</v>
+        <v>124371443</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6638,10 +6638,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460932</v>
+        <v>460918</v>
       </c>
       <c r="R56" t="n">
-        <v>6873104</v>
+        <v>6873190</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6700,10 +6700,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124371705</v>
+        <v>124372101</v>
       </c>
       <c r="B57" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6712,38 +6712,47 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460910</v>
+        <v>460917</v>
       </c>
       <c r="R57" t="n">
-        <v>6873163</v>
+        <v>6873090</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6802,10 +6811,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372101</v>
+        <v>124371705</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6814,47 +6823,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460917</v>
+        <v>460910</v>
       </c>
       <c r="R58" t="n">
-        <v>6873090</v>
+        <v>6873163</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6913,7 +6913,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372344</v>
+        <v>124371364</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460971</v>
+        <v>460923</v>
       </c>
       <c r="R59" t="n">
-        <v>6873061</v>
+        <v>6873201</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124373016</v>
+        <v>124372853</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461036</v>
+        <v>461025</v>
       </c>
       <c r="R60" t="n">
-        <v>6873063</v>
+        <v>6873087</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124371984</v>
+        <v>124372344</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460918</v>
+        <v>460971</v>
       </c>
       <c r="R61" t="n">
-        <v>6873097</v>
+        <v>6873061</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124371956</v>
+        <v>124371186</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460916</v>
+        <v>460943</v>
       </c>
       <c r="R62" t="n">
-        <v>6873108</v>
+        <v>6873209</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372853</v>
+        <v>124371241</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461025</v>
+        <v>460930</v>
       </c>
       <c r="R63" t="n">
-        <v>6873087</v>
+        <v>6873206</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124371443</v>
+        <v>124371658</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460918</v>
+        <v>460910</v>
       </c>
       <c r="R64" t="n">
-        <v>6873190</v>
+        <v>6873163</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124371241</v>
+        <v>124371956</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460930</v>
+        <v>460916</v>
       </c>
       <c r="R65" t="n">
-        <v>6873206</v>
+        <v>6873108</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371364</v>
+        <v>124371984</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460923</v>
+        <v>460918</v>
       </c>
       <c r="R66" t="n">
-        <v>6873201</v>
+        <v>6873097</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124371186</v>
+        <v>124372124</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460943</v>
+        <v>460923</v>
       </c>
       <c r="R67" t="n">
-        <v>6873209</v>
+        <v>6873105</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124373016</v>
+        <v>124372124</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461036</v>
+        <v>460923</v>
       </c>
       <c r="R54" t="n">
-        <v>6873063</v>
+        <v>6873105</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124372157</v>
+        <v>124371984</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460932</v>
+        <v>460918</v>
       </c>
       <c r="R55" t="n">
-        <v>6873104</v>
+        <v>6873097</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6700,7 +6700,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372101</v>
+        <v>124372344</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460917</v>
+        <v>460971</v>
       </c>
       <c r="R57" t="n">
-        <v>6873090</v>
+        <v>6873061</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6811,10 +6811,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124371705</v>
+        <v>124371956</v>
       </c>
       <c r="B58" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6823,38 +6823,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460910</v>
+        <v>460916</v>
       </c>
       <c r="R58" t="n">
-        <v>6873163</v>
+        <v>6873108</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6913,10 +6922,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124371364</v>
+        <v>124371705</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6925,47 +6934,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460923</v>
+        <v>460910</v>
       </c>
       <c r="R59" t="n">
-        <v>6873201</v>
+        <v>6873163</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372853</v>
+        <v>124372157</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461025</v>
+        <v>460932</v>
       </c>
       <c r="R60" t="n">
-        <v>6873087</v>
+        <v>6873104</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372344</v>
+        <v>124372853</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460971</v>
+        <v>461025</v>
       </c>
       <c r="R61" t="n">
-        <v>6873061</v>
+        <v>6873087</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124371186</v>
+        <v>124373016</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460943</v>
+        <v>461036</v>
       </c>
       <c r="R62" t="n">
-        <v>6873209</v>
+        <v>6873063</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124371241</v>
+        <v>124371658</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460930</v>
+        <v>460910</v>
       </c>
       <c r="R63" t="n">
-        <v>6873206</v>
+        <v>6873163</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124371658</v>
+        <v>124371364</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460910</v>
+        <v>460923</v>
       </c>
       <c r="R64" t="n">
-        <v>6873163</v>
+        <v>6873201</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124371956</v>
+        <v>124372101</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460916</v>
+        <v>460917</v>
       </c>
       <c r="R65" t="n">
-        <v>6873108</v>
+        <v>6873090</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371984</v>
+        <v>124371186</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460918</v>
+        <v>460943</v>
       </c>
       <c r="R66" t="n">
-        <v>6873097</v>
+        <v>6873209</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372124</v>
+        <v>124371241</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460923</v>
+        <v>460930</v>
       </c>
       <c r="R67" t="n">
-        <v>6873105</v>
+        <v>6873206</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124372124</v>
+        <v>124371443</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460923</v>
+        <v>460918</v>
       </c>
       <c r="R54" t="n">
-        <v>6873105</v>
+        <v>6873190</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124371984</v>
+        <v>124371705</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6490,47 +6490,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460918</v>
+        <v>460910</v>
       </c>
       <c r="R55" t="n">
-        <v>6873097</v>
+        <v>6873163</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6589,7 +6580,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124371443</v>
+        <v>124371364</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6624,7 +6615,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6638,10 +6629,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460918</v>
+        <v>460923</v>
       </c>
       <c r="R56" t="n">
-        <v>6873190</v>
+        <v>6873201</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6700,7 +6691,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372344</v>
+        <v>124372124</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6735,7 +6726,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6749,10 +6740,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460971</v>
+        <v>460923</v>
       </c>
       <c r="R57" t="n">
-        <v>6873061</v>
+        <v>6873105</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6811,7 +6802,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124371956</v>
+        <v>124372101</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6860,10 +6851,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460916</v>
+        <v>460917</v>
       </c>
       <c r="R58" t="n">
-        <v>6873108</v>
+        <v>6873090</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6922,10 +6913,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124371705</v>
+        <v>124371956</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6934,38 +6925,47 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460910</v>
+        <v>460916</v>
       </c>
       <c r="R59" t="n">
-        <v>6873163</v>
+        <v>6873108</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372157</v>
+        <v>124372344</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460932</v>
+        <v>460971</v>
       </c>
       <c r="R60" t="n">
-        <v>6873104</v>
+        <v>6873061</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372853</v>
+        <v>124371241</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461025</v>
+        <v>460930</v>
       </c>
       <c r="R61" t="n">
-        <v>6873087</v>
+        <v>6873206</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124373016</v>
+        <v>124371658</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461036</v>
+        <v>460910</v>
       </c>
       <c r="R62" t="n">
-        <v>6873063</v>
+        <v>6873163</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124371658</v>
+        <v>124373016</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460910</v>
+        <v>461036</v>
       </c>
       <c r="R63" t="n">
-        <v>6873163</v>
+        <v>6873063</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124371364</v>
+        <v>124371984</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460923</v>
+        <v>460918</v>
       </c>
       <c r="R64" t="n">
-        <v>6873201</v>
+        <v>6873097</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372101</v>
+        <v>124371186</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460917</v>
+        <v>460943</v>
       </c>
       <c r="R65" t="n">
-        <v>6873090</v>
+        <v>6873209</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371186</v>
+        <v>124372157</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460943</v>
+        <v>460932</v>
       </c>
       <c r="R66" t="n">
-        <v>6873209</v>
+        <v>6873104</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124371241</v>
+        <v>124372853</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460930</v>
+        <v>461025</v>
       </c>
       <c r="R67" t="n">
-        <v>6873206</v>
+        <v>6873087</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -6367,7 +6367,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124371443</v>
+        <v>124371186</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460918</v>
+        <v>460943</v>
       </c>
       <c r="R54" t="n">
-        <v>6873190</v>
+        <v>6873209</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124371705</v>
+        <v>124372101</v>
       </c>
       <c r="B55" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6490,38 +6490,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460910</v>
+        <v>460917</v>
       </c>
       <c r="R55" t="n">
-        <v>6873163</v>
+        <v>6873090</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6580,7 +6589,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124371364</v>
+        <v>124371443</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6615,7 +6624,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6629,10 +6638,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460923</v>
+        <v>460918</v>
       </c>
       <c r="R56" t="n">
-        <v>6873201</v>
+        <v>6873190</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6691,7 +6700,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372124</v>
+        <v>124373016</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6726,7 +6735,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6740,10 +6749,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460923</v>
+        <v>461036</v>
       </c>
       <c r="R57" t="n">
-        <v>6873105</v>
+        <v>6873063</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6802,7 +6811,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372101</v>
+        <v>124372344</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6837,7 +6846,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6851,10 +6860,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460917</v>
+        <v>460971</v>
       </c>
       <c r="R58" t="n">
-        <v>6873090</v>
+        <v>6873061</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6913,7 +6922,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124371956</v>
+        <v>124371241</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6948,7 +6957,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6962,10 +6971,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460916</v>
+        <v>460930</v>
       </c>
       <c r="R59" t="n">
-        <v>6873108</v>
+        <v>6873206</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7024,10 +7033,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372344</v>
+        <v>124371705</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7036,47 +7045,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460971</v>
+        <v>460910</v>
       </c>
       <c r="R60" t="n">
-        <v>6873061</v>
+        <v>6873163</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7135,7 +7135,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124371241</v>
+        <v>124372853</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460930</v>
+        <v>461025</v>
       </c>
       <c r="R61" t="n">
-        <v>6873206</v>
+        <v>6873087</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124371658</v>
+        <v>124371984</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460910</v>
+        <v>460918</v>
       </c>
       <c r="R62" t="n">
-        <v>6873163</v>
+        <v>6873097</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124373016</v>
+        <v>124372124</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461036</v>
+        <v>460923</v>
       </c>
       <c r="R63" t="n">
-        <v>6873063</v>
+        <v>6873105</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124371984</v>
+        <v>124371956</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460918</v>
+        <v>460916</v>
       </c>
       <c r="R64" t="n">
-        <v>6873097</v>
+        <v>6873108</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124371186</v>
+        <v>124372157</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460943</v>
+        <v>460932</v>
       </c>
       <c r="R65" t="n">
-        <v>6873209</v>
+        <v>6873104</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372157</v>
+        <v>124371364</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460932</v>
+        <v>460923</v>
       </c>
       <c r="R66" t="n">
-        <v>6873104</v>
+        <v>6873201</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372853</v>
+        <v>124371658</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461025</v>
+        <v>460910</v>
       </c>
       <c r="R67" t="n">
-        <v>6873087</v>
+        <v>6873163</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7910,6 +7910,111 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127649445</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Risbrunnsberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>460895</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6872870</v>
+      </c>
+      <c r="S68" t="n">
+        <v>50</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -7915,7 +7915,7 @@
         <v>127649445</v>
       </c>
       <c r="B68" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -7915,7 +7915,7 @@
         <v>127649445</v>
       </c>
       <c r="B68" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -7915,7 +7915,7 @@
         <v>127649445</v>
       </c>
       <c r="B68" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121333575</v>
+        <v>121587355</v>
       </c>
       <c r="B2" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461081</v>
+        <v>460722</v>
       </c>
       <c r="R2" t="n">
-        <v>6872891</v>
+        <v>6873319</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121333520</v>
+        <v>121587612</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461096</v>
+        <v>460706</v>
       </c>
       <c r="R3" t="n">
-        <v>6872904</v>
+        <v>6873222</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Intill basväg för skogsbruk.</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121333407</v>
+        <v>123968480</v>
       </c>
       <c r="B4" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461111</v>
+        <v>461161</v>
       </c>
       <c r="R4" t="n">
-        <v>6872947</v>
+        <v>6873068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121587377</v>
+        <v>124371705</v>
       </c>
       <c r="B5" t="n">
-        <v>78711</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460722</v>
+        <v>460910</v>
       </c>
       <c r="R5" t="n">
-        <v>6873319</v>
+        <v>6873163</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121587355</v>
+        <v>121333916</v>
       </c>
       <c r="B6" t="n">
-        <v>78663</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460722</v>
+        <v>460883</v>
       </c>
       <c r="R6" t="n">
-        <v>6873319</v>
+        <v>6873041</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1158,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121587594</v>
+        <v>121587377</v>
       </c>
       <c r="B7" t="n">
-        <v>78365</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460711</v>
+        <v>460722</v>
       </c>
       <c r="R7" t="n">
-        <v>6873214</v>
+        <v>6873319</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121587612</v>
+        <v>121333804</v>
       </c>
       <c r="B8" t="n">
-        <v>78663</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460706</v>
+        <v>460876</v>
       </c>
       <c r="R8" t="n">
-        <v>6873222</v>
+        <v>6873005</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,59 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123728124</v>
+        <v>121333575</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460506</v>
+        <v>461081</v>
       </c>
       <c r="R9" t="n">
-        <v>6873405</v>
+        <v>6872891</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1473,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,59 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123725467</v>
+        <v>121587594</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460583</v>
+        <v>460711</v>
       </c>
       <c r="R10" t="n">
-        <v>6873497</v>
+        <v>6873214</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1584,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,59 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123724854</v>
+        <v>121333407</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460566</v>
+        <v>461111</v>
       </c>
       <c r="R11" t="n">
-        <v>6873509</v>
+        <v>6872947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,59 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123728023</v>
+        <v>121333520</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460507</v>
+        <v>461096</v>
       </c>
       <c r="R12" t="n">
-        <v>6873398</v>
+        <v>6872904</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1806,12 +1710,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Intill basväg för skogsbruk.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,59 +1747,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123725130</v>
+        <v>121333818</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460567</v>
+        <v>460875</v>
       </c>
       <c r="R13" t="n">
-        <v>6873501</v>
+        <v>6873008</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1917,12 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,59 +1844,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123726451</v>
+        <v>121334000</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460627</v>
+        <v>460893</v>
       </c>
       <c r="R14" t="n">
-        <v>6873378</v>
+        <v>6872985</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2028,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,59 +1941,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123726535</v>
+        <v>123972174</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460596</v>
+        <v>460835</v>
       </c>
       <c r="R15" t="n">
-        <v>6873386</v>
+        <v>6872866</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2139,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,59 +2038,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123725365</v>
+        <v>123972942</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460570</v>
+        <v>460773</v>
       </c>
       <c r="R16" t="n">
-        <v>6873478</v>
+        <v>6872915</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2250,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,62 +2135,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123728236</v>
+        <v>127649445</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hjd</t>
+          <t>Risbrunnsberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460536</v>
+        <v>460895</v>
       </c>
       <c r="R17" t="n">
-        <v>6873468</v>
+        <v>6872870</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2361,12 +2208,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,27 +2228,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123972924</v>
+        <v>123724854</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,14 +2280,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460753</v>
+        <v>460566</v>
       </c>
       <c r="R18" t="n">
-        <v>6872934</v>
+        <v>6873509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,12 +2314,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,15 +2346,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123969532</v>
+        <v>123725130</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,14 +2386,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461139</v>
+        <v>460567</v>
       </c>
       <c r="R19" t="n">
-        <v>6873011</v>
+        <v>6873501</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2583,12 +2420,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,15 +2452,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123971703</v>
+        <v>123725365</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,7 +2482,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2660,14 +2492,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460841</v>
+        <v>460570</v>
       </c>
       <c r="R20" t="n">
-        <v>6872822</v>
+        <v>6873478</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2694,12 +2526,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,15 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123968641</v>
+        <v>123725467</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2761,7 +2588,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2771,14 +2598,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461153</v>
+        <v>460583</v>
       </c>
       <c r="R21" t="n">
-        <v>6873049</v>
+        <v>6873497</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2805,12 +2632,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,15 +2664,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123971441</v>
+        <v>123725701</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,7 +2694,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2882,14 +2704,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460898</v>
+        <v>460611</v>
       </c>
       <c r="R22" t="n">
-        <v>6872865</v>
+        <v>6873474</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2916,17 +2738,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färdigställd basväg 10 meter från plantorna.</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2953,50 +2770,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123972174</v>
+        <v>123726008</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460835</v>
+        <v>460604</v>
       </c>
       <c r="R23" t="n">
-        <v>6872866</v>
+        <v>6873475</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3023,12 +2835,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,15 +2867,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123971547</v>
+        <v>123726451</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,7 +2897,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3100,14 +2907,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460857</v>
+        <v>460627</v>
       </c>
       <c r="R24" t="n">
-        <v>6872836</v>
+        <v>6873378</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3134,12 +2941,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,15 +2973,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123970760</v>
+        <v>123726535</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3003,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3211,14 +3013,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461123</v>
+        <v>460596</v>
       </c>
       <c r="R25" t="n">
-        <v>6872900</v>
+        <v>6873386</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3245,12 +3047,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,15 +3079,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123972957</v>
+        <v>123727514</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3312,7 +3109,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3322,14 +3119,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460773</v>
+        <v>460514</v>
       </c>
       <c r="R26" t="n">
-        <v>6872915</v>
+        <v>6873343</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3356,12 +3153,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,15 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123971888</v>
+        <v>123727536</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3423,7 +3215,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3433,14 +3225,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460825</v>
+        <v>460497</v>
       </c>
       <c r="R27" t="n">
-        <v>6872838</v>
+        <v>6873347</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3467,12 +3259,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3499,15 +3291,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123970349</v>
+        <v>123727612</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3321,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3544,17 +3331,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461128</v>
+        <v>460507</v>
       </c>
       <c r="R28" t="n">
-        <v>6872966</v>
+        <v>6873355</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3578,12 +3365,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3610,15 +3397,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123972974</v>
+        <v>123728023</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3645,7 +3427,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3655,14 +3437,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460794</v>
+        <v>460507</v>
       </c>
       <c r="R29" t="n">
-        <v>6872937</v>
+        <v>6873398</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3689,12 +3471,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,15 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123970431</v>
+        <v>123728124</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,7 +3533,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3766,14 +3543,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461110</v>
+        <v>460506</v>
       </c>
       <c r="R30" t="n">
-        <v>6872966</v>
+        <v>6873405</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3800,12 +3577,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3832,15 +3609,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123970830</v>
+        <v>123728236</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,7 +3639,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3877,14 +3649,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+          <t>Råbäcken, Råbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461105</v>
+        <v>460536</v>
       </c>
       <c r="R31" t="n">
-        <v>6872902</v>
+        <v>6873468</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3911,12 +3683,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3943,15 +3715,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123970952</v>
+        <v>123968641</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3978,7 +3745,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3992,10 +3759,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461073</v>
+        <v>461153</v>
       </c>
       <c r="R32" t="n">
-        <v>6872885</v>
+        <v>6873049</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4054,15 +3821,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123970673</v>
+        <v>123968964</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4089,7 +3851,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4103,10 +3865,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461113</v>
+        <v>461159</v>
       </c>
       <c r="R33" t="n">
-        <v>6872925</v>
+        <v>6872976</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4165,15 +3927,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123972218</v>
+        <v>123969194</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4200,7 +3957,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4214,13 +3971,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460794</v>
+        <v>461139</v>
       </c>
       <c r="R34" t="n">
-        <v>6872877</v>
+        <v>6872988</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4276,15 +4033,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123970513</v>
+        <v>123969327</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4311,7 +4063,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4325,13 +4077,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461128</v>
+        <v>461130</v>
       </c>
       <c r="R35" t="n">
-        <v>6872930</v>
+        <v>6872999</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4387,15 +4139,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123971836</v>
+        <v>123969532</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4169,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4436,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460837</v>
+        <v>461139</v>
       </c>
       <c r="R36" t="n">
-        <v>6872871</v>
+        <v>6873011</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4498,15 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123969902</v>
+        <v>123969726</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4533,7 +4275,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4547,13 +4289,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461144</v>
+        <v>461123</v>
       </c>
       <c r="R37" t="n">
-        <v>6872958</v>
+        <v>6872994</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4609,15 +4351,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123973080</v>
+        <v>123969799</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4644,7 +4381,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4658,10 +4395,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460847</v>
+        <v>461132</v>
       </c>
       <c r="R38" t="n">
-        <v>6872983</v>
+        <v>6872951</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4723,12 +4460,7 @@
         <v>123969829</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4831,15 +4563,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123972193</v>
+        <v>123969902</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4866,7 +4593,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4880,13 +4607,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460814</v>
+        <v>461144</v>
       </c>
       <c r="R40" t="n">
-        <v>6872895</v>
+        <v>6872958</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4942,15 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123970610</v>
+        <v>123970349</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4977,7 +4699,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4991,13 +4713,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461109</v>
+        <v>461128</v>
       </c>
       <c r="R41" t="n">
-        <v>6872931</v>
+        <v>6872966</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5053,15 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123971590</v>
+        <v>123970431</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5088,7 +4805,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5102,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460875</v>
+        <v>461110</v>
       </c>
       <c r="R42" t="n">
-        <v>6872840</v>
+        <v>6872966</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5164,50 +4881,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123972942</v>
+        <v>123970513</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460773</v>
+        <v>461128</v>
       </c>
       <c r="R43" t="n">
-        <v>6872915</v>
+        <v>6872930</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5266,15 +4987,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123973004</v>
+        <v>123970610</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5315,10 +5031,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460809</v>
+        <v>461109</v>
       </c>
       <c r="R44" t="n">
-        <v>6872950</v>
+        <v>6872931</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5377,53 +5093,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123968480</v>
+        <v>123970673</v>
       </c>
       <c r="B45" t="n">
-        <v>78842</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461161</v>
+        <v>461113</v>
       </c>
       <c r="R45" t="n">
-        <v>6873068</v>
+        <v>6872925</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5479,15 +5199,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123969327</v>
+        <v>123970760</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5514,7 +5229,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5528,13 +5243,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461130</v>
+        <v>461123</v>
       </c>
       <c r="R46" t="n">
-        <v>6872999</v>
+        <v>6872900</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5590,15 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123970979</v>
+        <v>123970830</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5639,10 +5349,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461072</v>
+        <v>461105</v>
       </c>
       <c r="R47" t="n">
-        <v>6872887</v>
+        <v>6872902</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5701,15 +5411,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123972590</v>
+        <v>123970875</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5736,7 +5441,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5750,10 +5455,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460772</v>
+        <v>461120</v>
       </c>
       <c r="R48" t="n">
-        <v>6872900</v>
+        <v>6872882</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5812,15 +5517,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123969194</v>
+        <v>123970907</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5847,7 +5547,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5861,10 +5561,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461139</v>
+        <v>461113</v>
       </c>
       <c r="R49" t="n">
-        <v>6872988</v>
+        <v>6872871</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5923,15 +5623,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123970875</v>
+        <v>123970952</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5972,10 +5667,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461120</v>
+        <v>461073</v>
       </c>
       <c r="R50" t="n">
-        <v>6872882</v>
+        <v>6872885</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6034,15 +5729,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123969726</v>
+        <v>123970979</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6083,13 +5773,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461123</v>
+        <v>461072</v>
       </c>
       <c r="R51" t="n">
-        <v>6872994</v>
+        <v>6872887</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6145,15 +5835,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123969799</v>
+        <v>123971441</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6180,7 +5865,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6194,10 +5879,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461132</v>
+        <v>460898</v>
       </c>
       <c r="R52" t="n">
-        <v>6872951</v>
+        <v>6872865</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6230,6 +5915,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färdigställd basväg 10 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6256,15 +5946,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123972041</v>
+        <v>123971547</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +5976,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6305,10 +5990,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460743</v>
+        <v>460857</v>
       </c>
       <c r="R53" t="n">
-        <v>6872768</v>
+        <v>6872836</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6367,15 +6052,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124371186</v>
+        <v>123971590</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6402,7 +6082,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6416,10 +6096,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460943</v>
+        <v>460875</v>
       </c>
       <c r="R54" t="n">
-        <v>6873209</v>
+        <v>6872840</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6446,12 +6126,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6478,15 +6158,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124372101</v>
+        <v>123971703</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6527,10 +6202,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460917</v>
+        <v>460841</v>
       </c>
       <c r="R55" t="n">
-        <v>6873090</v>
+        <v>6872822</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6557,12 +6232,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6589,15 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124371443</v>
+        <v>123971732</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6624,7 +6294,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6638,10 +6308,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460918</v>
+        <v>460857</v>
       </c>
       <c r="R56" t="n">
-        <v>6873190</v>
+        <v>6872807</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6668,12 +6338,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6700,15 +6370,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124373016</v>
+        <v>123971790</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6735,7 +6400,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6749,10 +6414,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461036</v>
+        <v>460875</v>
       </c>
       <c r="R57" t="n">
-        <v>6873063</v>
+        <v>6872818</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6779,12 +6444,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6811,15 +6476,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372344</v>
+        <v>123971836</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6846,7 +6506,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6860,10 +6520,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460971</v>
+        <v>460837</v>
       </c>
       <c r="R58" t="n">
-        <v>6873061</v>
+        <v>6872871</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6890,12 +6550,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6922,15 +6582,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124371241</v>
+        <v>123971888</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6957,7 +6612,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6971,10 +6626,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460930</v>
+        <v>460825</v>
       </c>
       <c r="R59" t="n">
-        <v>6873206</v>
+        <v>6872838</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7001,12 +6656,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7033,50 +6688,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124371705</v>
+        <v>123971964</v>
       </c>
       <c r="B60" t="n">
-        <v>78842</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460910</v>
+        <v>460798</v>
       </c>
       <c r="R60" t="n">
-        <v>6873163</v>
+        <v>6872831</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7103,12 +6762,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7135,15 +6794,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372853</v>
+        <v>123971983</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7170,7 +6824,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7184,10 +6838,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461025</v>
+        <v>460788</v>
       </c>
       <c r="R61" t="n">
-        <v>6873087</v>
+        <v>6872823</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7214,12 +6868,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7246,15 +6900,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124371984</v>
+        <v>123972041</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7295,10 +6944,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460918</v>
+        <v>460743</v>
       </c>
       <c r="R62" t="n">
-        <v>6873097</v>
+        <v>6872768</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7325,12 +6974,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7357,15 +7006,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372124</v>
+        <v>123972193</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7392,7 +7036,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7406,13 +7050,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460923</v>
+        <v>460814</v>
       </c>
       <c r="R63" t="n">
-        <v>6873105</v>
+        <v>6872895</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7436,12 +7080,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7468,15 +7112,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124371956</v>
+        <v>123972218</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7503,7 +7142,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7517,13 +7156,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>460916</v>
+        <v>460794</v>
       </c>
       <c r="R64" t="n">
-        <v>6873108</v>
+        <v>6872877</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7547,12 +7186,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7579,15 +7218,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372157</v>
+        <v>123972590</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7614,7 +7248,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7628,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>460932</v>
+        <v>460772</v>
       </c>
       <c r="R65" t="n">
-        <v>6873104</v>
+        <v>6872900</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7658,12 +7292,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7690,15 +7324,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124371364</v>
+        <v>123972924</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7739,13 +7368,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>460923</v>
+        <v>460753</v>
       </c>
       <c r="R66" t="n">
-        <v>6873201</v>
+        <v>6872934</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7769,12 +7398,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7801,15 +7430,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124371658</v>
+        <v>123972957</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7836,7 +7460,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7850,10 +7474,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>460910</v>
+        <v>460773</v>
       </c>
       <c r="R67" t="n">
-        <v>6873163</v>
+        <v>6872915</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7880,12 +7504,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7912,56 +7536,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127649445</v>
+        <v>123972974</v>
       </c>
       <c r="B68" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Risbrunnsberget, Hjd</t>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>460895</v>
+        <v>460794</v>
       </c>
       <c r="R68" t="n">
-        <v>6872870</v>
+        <v>6872937</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7985,12 +7610,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8005,15 +7630,1702 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>123973004</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>460809</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6872950</v>
+      </c>
+      <c r="S69" t="n">
+        <v>20</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>123973080</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>460847</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6872983</v>
+      </c>
+      <c r="S70" t="n">
+        <v>20</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>124371186</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>460943</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6873209</v>
+      </c>
+      <c r="S71" t="n">
+        <v>20</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>124371241</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>460930</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6873206</v>
+      </c>
+      <c r="S72" t="n">
+        <v>20</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>124371364</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>460923</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6873201</v>
+      </c>
+      <c r="S73" t="n">
+        <v>20</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>124371443</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>460918</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6873190</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>124371658</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>460910</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6873163</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>124371956</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>460916</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6873108</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>124371984</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>460918</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6873097</v>
+      </c>
+      <c r="S77" t="n">
+        <v>20</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>124372101</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>460917</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6873090</v>
+      </c>
+      <c r="S78" t="n">
+        <v>20</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>124372124</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>460923</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6873105</v>
+      </c>
+      <c r="S79" t="n">
+        <v>20</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>124372157</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>460932</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6873104</v>
+      </c>
+      <c r="S80" t="n">
+        <v>20</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>124372344</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>460971</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6873061</v>
+      </c>
+      <c r="S81" t="n">
+        <v>20</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>124372853</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>461025</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6873087</v>
+      </c>
+      <c r="S82" t="n">
+        <v>20</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>124373016</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>461036</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6873063</v>
+      </c>
+      <c r="S83" t="n">
+        <v>20</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>121333977</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kattyggeldalen, Kattyggeldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>460892</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6873043</v>
+      </c>
+      <c r="S84" t="n">
+        <v>20</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56468-2024 artfynd.xlsx
+++ b/artfynd/A 56468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121587355</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121587612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123968480</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124371705</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121333916</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121587377</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121333804</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121333575</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121587594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121333407</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121333520</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121333818</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121334000</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123972174</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123972942</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2237,6 +2317,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127649445</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2343,6 +2428,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123724854</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2449,6 +2539,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725130</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2555,6 +2650,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725365</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725467</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2767,6 +2872,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725701</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2864,6 +2974,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123726008</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2970,6 +3085,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123726451</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3076,6 +3196,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123726535</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3182,6 +3307,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123727514</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3288,6 +3418,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123727536</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3394,6 +3529,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123727612</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123728023</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3606,6 +3751,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123728124</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3712,6 +3862,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123728236</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3818,6 +3973,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123968641</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3924,6 +4084,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123968964</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4030,6 +4195,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123969194</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4136,6 +4306,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123969327</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4242,6 +4417,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123969532</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4348,6 +4528,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123969726</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4454,6 +4639,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123969799</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4560,6 +4750,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123969829</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4666,6 +4861,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123969902</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4772,6 +4972,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970349</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4878,6 +5083,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970431</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4984,6 +5194,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970513</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5090,6 +5305,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970610</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5196,6 +5416,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970673</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5302,6 +5527,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970760</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5408,6 +5638,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970830</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5514,6 +5749,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970875</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5620,6 +5860,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970907</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5726,6 +5971,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970952</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5832,6 +6082,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970979</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5943,6 +6198,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971441</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6049,6 +6309,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971547</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6155,6 +6420,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971590</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6261,6 +6531,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971703</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6367,6 +6642,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971732</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6473,6 +6753,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971790</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6579,6 +6864,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971836</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6685,6 +6975,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971888</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6791,6 +7086,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971964</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6897,6 +7197,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123971983</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7003,6 +7308,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123972041</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7109,6 +7419,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123972193</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7215,6 +7530,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123972218</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7321,6 +7641,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123972590</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7427,6 +7752,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123972924</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7533,6 +7863,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123972957</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7639,6 +7974,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123972974</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7745,6 +8085,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123973004</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7851,6 +8196,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123973080</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7957,6 +8307,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124371186</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8063,6 +8418,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124371241</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8169,6 +8529,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124371364</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8275,6 +8640,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124371443</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8381,6 +8751,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124371658</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8487,6 +8862,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124371956</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8593,6 +8973,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124371984</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8699,6 +9084,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124372101</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8805,6 +9195,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124372124</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8911,6 +9306,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124372157</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9017,6 +9417,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124372344</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9123,6 +9528,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124372853</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9229,6 +9639,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124373016</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9326,8 +9741,98 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121333977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>